--- a/changes/9mm-ammo-super.xlsx
+++ b/changes/9mm-ammo-super.xlsx
@@ -1,44 +1,90 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yifan\Documents\deadline-balancing\changes\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44839988-6DF1-4A3D-A86D-9893466D0229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="545-ammo" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Model" sheetId="2" r:id="rId6"/>
+    <sheet name="545-ammo" sheetId="1" r:id="rId1"/>
+    <sheet name="Model" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment authorId="0" ref="T2">
+    <comment ref="M2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
-        <t xml:space="preserve">[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Carlito"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Direct values from calibers.csv. Edit these cells on this sheet to tune the ammo model.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Carlito"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Damage formula: MAX(MIN(a × distance + b, c) × d, 0). Distances and weights are on the Model sheet.</t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="AJ2">
+    <comment ref="AJ2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
-        <t xml:space="preserve">[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Carlito"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Linearly interpolates effective velocity between pen_low/pen_high and clamps to those endpoints.</t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="M2">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Direct values from calibers.csv. Edit these cells on this sheet to tune the ammo model.</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -46,17 +92,25 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment authorId="0" ref="B20">
+    <comment ref="B20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
-        <t xml:space="preserve">[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Carlito"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Damage distance weights should total 100%.</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -390,7 +444,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
@@ -398,53 +452,56 @@
   </numFmts>
   <fonts count="10">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Carlito"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="16.0"/>
+      <sz val="16"/>
       <color rgb="FFFFFFFF"/>
       <name val="Play"/>
     </font>
-    <font/>
     <font>
-      <sz val="10.0"/>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF1F2933"/>
       <name val="Aptos"/>
     </font>
     <font>
       <b/>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF1F2933"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="9.0"/>
+      <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos"/>
     </font>
     <font>
       <b/>
-      <sz val="9.0"/>
+      <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="9.0"/>
+      <sz val="9"/>
       <color rgb="FF1F2933"/>
       <name val="Aptos"/>
     </font>
     <font>
-      <sz val="9.0"/>
+      <sz val="9"/>
       <color rgb="FF1F2933"/>
       <name val="Arial"/>
     </font>
@@ -454,7 +511,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -530,20 +587,33 @@
     </fill>
   </fills>
   <borders count="11">
-    <border/>
     <border>
       <left/>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -552,6 +622,7 @@
       <bottom style="thin">
         <color rgb="FFD8E0E7"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -562,25 +633,10 @@
       <bottom style="thin">
         <color rgb="FFD8E0E7"/>
       </bottom>
-    </border>
-    <border>
-      <top style="thin">
-        <color rgb="FFD8E0E7"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD8E0E7"/>
-      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
-      <top style="thin">
-        <color rgb="FFD8E0E7"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD8E0E7"/>
-      </bottom>
-    </border>
-    <border>
       <right/>
       <top style="thin">
         <color rgb="FFD8E0E7"/>
@@ -588,12 +644,36 @@
       <bottom style="thin">
         <color rgb="FFD8E0E7"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD8E0E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD8E0E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD8E0E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD8E0E7"/>
+      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -602,230 +682,201 @@
         <color rgb="FFD8E0E7"/>
       </top>
       <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="70">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="3" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="4" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="1" fontId="8" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="2" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="5" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="2" fontId="8" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="4" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="4" fontId="5" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="3" numFmtId="2" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="13" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="12" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="13" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="7" fillId="5" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="9" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="7" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="5" fillId="7" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="7" fontId="3" numFmtId="164" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="9" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="10" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="7" fontId="3" numFmtId="165" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="4" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="7" fontId="3" numFmtId="166" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="7" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="2" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="3" numFmtId="165" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="11" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="5" fillId="11" fontId="3" numFmtId="165" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="10" fillId="11" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="10" fillId="11" fontId="3" numFmtId="165" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="4" fontId="8" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="4" fontId="9" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="4" fontId="8" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="4" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="12" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="12" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="12" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="13" fontId="8" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="12" fontId="9" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="12" fontId="8" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="12" fontId="9" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="13" fontId="8" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="7" fontId="9" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="7" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="11" fontId="8" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="4" fontId="9" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="4" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="10" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="10" fillId="4" fontId="9" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="10" fillId="4" fontId="9" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="10" fillId="4" fontId="8" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="10" fillId="4" fontId="8" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="10" fillId="4" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="10" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="10" fillId="4" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="10" fillId="12" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="10" fillId="13" fontId="8" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="10" fillId="12" fontId="9" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="10" fillId="13" fontId="8" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="10" fillId="7" fontId="9" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="10" fillId="7" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="10" fillId="11" fontId="8" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="4">
     <dxf>
-      <font/>
       <fill>
-        <patternFill patternType="none"/>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC1E4F5"/>
+          <bgColor rgb="FFC1E4F5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor theme="4"/>
           <bgColor theme="4"/>
         </patternFill>
       </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC1E4F5"/>
-          <bgColor rgb="FFC1E4F5"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border/>
     </dxf>
     <dxf>
       <border>
@@ -851,82 +902,78 @@
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle count="4" pivot="0" name="545-ammo-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    <tableStyle name="545-ammo-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="3"/>
+      <tableStyleElement type="headerRow" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A2:AR13" displayName="AmmoChangeSheet" name="AmmoChangeSheet" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="AmmoChangeSheet" displayName="AmmoChangeSheet" ref="A2:AR13">
   <tableColumns count="44">
-    <tableColumn name="name" id="1"/>
-    <tableColumn name="pretty_name" id="2"/>
-    <tableColumn name="ergonomics" id="3"/>
-    <tableColumn name="weight" id="4"/>
-    <tableColumn name="horizontal_recoil" id="5"/>
-    <tableColumn name="vertical_recoil" id="6"/>
-    <tableColumn name="barrel_deviation" id="7"/>
-    <tableColumn name="bullet_damage" id="8"/>
-    <tableColumn name="bullet_velocity" id="9"/>
-    <tableColumn name="fire_rate" id="10"/>
-    <tableColumn name="muzzle_loudness" id="11"/>
-    <tableColumn name="price" id="12"/>
-    <tableColumn name="damage_torso_a" id="13"/>
-    <tableColumn name="damage_torso_b" id="14"/>
-    <tableColumn name="damage_torso_c" id="15"/>
-    <tableColumn name="damage_torso_d" id="16"/>
-    <tableColumn name="damage_arm_d" id="17"/>
-    <tableColumn name="damage_leg_d" id="18"/>
-    <tableColumn name="damage_head_d" id="19"/>
-    <tableColumn name="damage_25" id="20"/>
-    <tableColumn name="damage_75" id="21"/>
-    <tableColumn name="damage_150" id="22"/>
-    <tableColumn name="damage_250" id="23"/>
-    <tableColumn name="damage_375" id="24"/>
-    <tableColumn name="damage_400" id="25"/>
-    <tableColumn name="damage_500" id="26"/>
-    <tableColumn name="weighted_damage" id="27"/>
-    <tableColumn name="velocity_drop" id="28"/>
-    <tableColumn name="suppression" id="29"/>
-    <tableColumn name="bullet_penetration_ability" id="30"/>
-    <tableColumn name="pen_low" id="31"/>
-    <tableColumn name="pen_high" id="32"/>
-    <tableColumn name="pen_velocity_low" id="33"/>
-    <tableColumn name="pen_velocity_high" id="34"/>
-    <tableColumn name="effective_velocity" id="35"/>
-    <tableColumn name="penetration" id="36"/>
-    <tableColumn name="calibers_row" id="37"/>
-    <tableColumn name="source_file" id="38"/>
-    <tableColumn name="balance_score" id="39"/>
-    <tableColumn name="damage_score" id="40"/>
-    <tableColumn name="velocity_drop_score" id="41"/>
-    <tableColumn name="suppression_score" id="42"/>
-    <tableColumn name="penetration_score" id="43"/>
-    <tableColumn name="strength" id="44"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="name"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="pretty_name"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="ergonomics"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="weight"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="horizontal_recoil"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="vertical_recoil"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="barrel_deviation"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="bullet_damage"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="bullet_velocity"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="fire_rate"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="muzzle_loudness"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="price"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="damage_torso_a"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="damage_torso_b"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="damage_torso_c"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="damage_torso_d"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="damage_arm_d"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="damage_leg_d"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="damage_head_d"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="damage_25"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="damage_75"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="damage_150"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="damage_250"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="damage_375"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="damage_400"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="damage_500"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="weighted_damage"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="velocity_drop"/>
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="suppression"/>
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="bullet_penetration_ability"/>
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="pen_low"/>
+    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="pen_high"/>
+    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="pen_velocity_low"/>
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="pen_velocity_high"/>
+    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" name="effective_velocity"/>
+    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0000-000024000000}" name="penetration"/>
+    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0000-000025000000}" name="calibers_row"/>
+    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0000-000026000000}" name="source_file"/>
+    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0000-000027000000}" name="balance_score"/>
+    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0000-000028000000}" name="damage_score"/>
+    <tableColumn id="41" xr3:uid="{00000000-0010-0000-0000-000029000000}" name="velocity_drop_score"/>
+    <tableColumn id="42" xr3:uid="{00000000-0010-0000-0000-00002A000000}" name="suppression_score"/>
+    <tableColumn id="43" xr3:uid="{00000000-0010-0000-0000-00002B000000}" name="penetration_score"/>
+    <tableColumn id="44" xr3:uid="{00000000-0010-0000-0000-00002C000000}" name="strength"/>
   </tableColumns>
-  <tableStyleInfo name="545-ammo-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="545-ammo-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1116,1823 +1163,1823 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AR1000"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="26.13"/>
-    <col customWidth="1" min="2" max="2" width="22.75"/>
-    <col customWidth="1" min="3" max="8" width="5.63"/>
-    <col customWidth="1" min="9" max="9" width="8.0"/>
-    <col customWidth="1" min="10" max="29" width="5.63"/>
-    <col customWidth="1" min="30" max="30" width="27.13"/>
-    <col customWidth="1" min="31" max="37" width="5.63"/>
-    <col customWidth="1" min="38" max="38" width="9.63"/>
-    <col customWidth="1" min="39" max="44" width="5.63"/>
+    <col min="1" max="1" width="26.125" customWidth="1"/>
+    <col min="2" max="2" width="22.75" customWidth="1"/>
+    <col min="3" max="8" width="5.625" customWidth="1"/>
+    <col min="9" max="9" width="8" customWidth="1"/>
+    <col min="10" max="29" width="5.625" customWidth="1"/>
+    <col min="30" max="30" width="27.125" customWidth="1"/>
+    <col min="31" max="37" width="5.625" customWidth="1"/>
+    <col min="38" max="38" width="9.625" customWidth="1"/>
+    <col min="39" max="44" width="5.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24.0" customHeight="1">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:44" ht="24" customHeight="1">
+      <c r="A1" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="16" t="s">
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="18"/>
-      <c r="R1" s="18"/>
-      <c r="S1" s="18"/>
-      <c r="T1" s="21" t="s">
+      <c r="N1" s="59"/>
+      <c r="O1" s="59"/>
+      <c r="P1" s="60"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+      <c r="T1" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
-      <c r="Z1" s="2"/>
-      <c r="AA1" s="3"/>
-      <c r="AB1" s="16" t="s">
+      <c r="U1" s="59"/>
+      <c r="V1" s="59"/>
+      <c r="W1" s="59"/>
+      <c r="X1" s="59"/>
+      <c r="Y1" s="59"/>
+      <c r="Z1" s="59"/>
+      <c r="AA1" s="60"/>
+      <c r="AB1" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="AC1" s="2"/>
-      <c r="AD1" s="2"/>
-      <c r="AE1" s="2"/>
-      <c r="AF1" s="2"/>
-      <c r="AG1" s="2"/>
-      <c r="AH1" s="3"/>
-      <c r="AI1" s="24" t="s">
+      <c r="AC1" s="59"/>
+      <c r="AD1" s="59"/>
+      <c r="AE1" s="59"/>
+      <c r="AF1" s="59"/>
+      <c r="AG1" s="59"/>
+      <c r="AH1" s="60"/>
+      <c r="AI1" s="69" t="s">
         <v>26</v>
       </c>
-      <c r="AJ1" s="3"/>
-      <c r="AK1" s="25" t="s">
+      <c r="AJ1" s="60"/>
+      <c r="AK1" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="AL1" s="3"/>
-      <c r="AM1" s="26" t="s">
+      <c r="AL1" s="60"/>
+      <c r="AM1" s="65" t="s">
         <v>30</v>
       </c>
-      <c r="AN1" s="2"/>
-      <c r="AO1" s="2"/>
-      <c r="AP1" s="2"/>
-      <c r="AQ1" s="2"/>
-      <c r="AR1" s="3"/>
+      <c r="AN1" s="59"/>
+      <c r="AO1" s="59"/>
+      <c r="AP1" s="59"/>
+      <c r="AQ1" s="59"/>
+      <c r="AR1" s="60"/>
     </row>
-    <row r="2" ht="45.75" customHeight="1">
-      <c r="A2" s="28" t="s">
+    <row r="2" spans="1:44" ht="45.75" customHeight="1">
+      <c r="A2" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="28" t="s">
+      <c r="D2" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="28" t="s">
+      <c r="E2" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="F2" s="28" t="s">
+      <c r="F2" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="G2" s="28" t="s">
+      <c r="G2" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="H2" s="28" t="s">
+      <c r="H2" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="I2" s="28" t="s">
+      <c r="I2" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="J2" s="28" t="s">
+      <c r="J2" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="K2" s="31" t="s">
+      <c r="K2" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="L2" s="28" t="s">
+      <c r="L2" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="M2" s="28" t="s">
+      <c r="M2" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="N2" s="28" t="s">
+      <c r="N2" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="O2" s="28" t="s">
+      <c r="O2" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="P2" s="28" t="s">
+      <c r="P2" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="Q2" s="28" t="s">
+      <c r="Q2" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="R2" s="28" t="s">
+      <c r="R2" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="S2" s="28" t="s">
+      <c r="S2" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="T2" s="28" t="s">
+      <c r="T2" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="U2" s="28" t="s">
+      <c r="U2" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="V2" s="28" t="s">
+      <c r="V2" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="W2" s="28" t="s">
+      <c r="W2" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="X2" s="28" t="s">
+      <c r="X2" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="Y2" s="28" t="s">
+      <c r="Y2" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="Z2" s="28" t="s">
+      <c r="Z2" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="AA2" s="28" t="s">
+      <c r="AA2" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="AB2" s="28" t="s">
+      <c r="AB2" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="AC2" s="28" t="s">
+      <c r="AC2" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="AD2" s="28" t="s">
+      <c r="AD2" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="AE2" s="28" t="s">
+      <c r="AE2" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="AF2" s="28" t="s">
+      <c r="AF2" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="AG2" s="28" t="s">
+      <c r="AG2" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="AH2" s="28" t="s">
+      <c r="AH2" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="AI2" s="28" t="s">
+      <c r="AI2" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="AJ2" s="28" t="s">
+      <c r="AJ2" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="AK2" s="28" t="s">
+      <c r="AK2" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="AL2" s="28" t="s">
+      <c r="AL2" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="AM2" s="28" t="s">
+      <c r="AM2" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="AN2" s="28" t="s">
+      <c r="AN2" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="AO2" s="28" t="s">
+      <c r="AO2" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="AP2" s="28" t="s">
+      <c r="AP2" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="AQ2" s="28" t="s">
+      <c r="AQ2" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="AR2" s="28" t="s">
+      <c r="AR2" s="16" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="37" t="s">
+    <row r="3" spans="1:44" ht="14.25" customHeight="1">
+      <c r="A3" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="38">
-        <v>0.0</v>
-      </c>
-      <c r="D3" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="E3" s="38">
-        <v>0.0</v>
-      </c>
-      <c r="F3" s="38">
-        <v>0.0</v>
-      </c>
-      <c r="G3" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H3" s="41"/>
-      <c r="I3" s="38">
+      <c r="C3" s="26">
+        <v>0</v>
+      </c>
+      <c r="D3" s="27">
+        <v>0</v>
+      </c>
+      <c r="E3" s="26">
+        <v>0</v>
+      </c>
+      <c r="F3" s="26">
+        <v>0</v>
+      </c>
+      <c r="G3" s="28">
+        <v>0</v>
+      </c>
+      <c r="H3" s="29"/>
+      <c r="I3" s="26">
         <v>0.02</v>
       </c>
-      <c r="J3" s="40"/>
-      <c r="K3" s="42"/>
-      <c r="L3" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="M3" s="43">
-        <v>-0.07</v>
-      </c>
-      <c r="N3" s="43">
-        <v>39.0</v>
-      </c>
-      <c r="O3" s="43">
+      <c r="J3" s="28"/>
+      <c r="K3" s="30"/>
+      <c r="L3" s="30">
+        <v>0</v>
+      </c>
+      <c r="M3" s="31">
+        <v>-7.0000000000000007E-2</v>
+      </c>
+      <c r="N3" s="31">
+        <v>39</v>
+      </c>
+      <c r="O3" s="31">
         <v>38.5</v>
       </c>
-      <c r="P3" s="43">
-        <v>1.0</v>
-      </c>
-      <c r="Q3" s="44">
+      <c r="P3" s="31">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="31">
         <v>0.3</v>
       </c>
-      <c r="R3" s="44">
+      <c r="R3" s="31">
         <v>0.5</v>
       </c>
-      <c r="S3" s="45">
-        <v>3.0</v>
-      </c>
-      <c r="T3" s="46">
+      <c r="S3" s="32">
+        <v>3</v>
+      </c>
+      <c r="T3" s="33">
         <f>MAX(MIN($M3*Model!$A$13+$N3,$O3)*$P3,0)</f>
         <v>37.25</v>
       </c>
-      <c r="U3" s="46">
+      <c r="U3" s="33">
         <f>MAX(MIN($M3*Model!$A$14+$N3,$O3)*$P3,0)</f>
         <v>33.75</v>
       </c>
-      <c r="V3" s="46">
+      <c r="V3" s="33">
         <f>MAX(MIN($M3*Model!$A$15+$N3,$O3)*$P3,0)</f>
         <v>28.5</v>
       </c>
-      <c r="W3" s="46">
+      <c r="W3" s="33">
         <f>MAX(MIN($M3*Model!$A$16+$N3,$O3)*$P3,0)</f>
         <v>21.5</v>
       </c>
-      <c r="X3" s="46">
+      <c r="X3" s="33">
         <f>MAX(MIN($M3*Model!$A$17+$N3,$O3)*$P3,0)</f>
         <v>38.5</v>
       </c>
-      <c r="Y3" s="46">
+      <c r="Y3" s="33">
         <f>MAX(MIN($M3*Model!$A$18+$N3,$O3)*$P3,0)</f>
         <v>38.5</v>
       </c>
-      <c r="Z3" s="46">
+      <c r="Z3" s="33">
         <f>MAX(MIN($M3*Model!$A$19+$N3,$O3)*$P3,0)</f>
         <v>38.5</v>
       </c>
-      <c r="AA3" s="46">
+      <c r="AA3" s="33">
         <f>T3*Model!$B$13+U3*Model!$B$14+V3*Model!$B$15+W3*Model!$B$16+X3*Model!$B$17+Y3*Model!$B$18+Z3*Model!$B$19</f>
         <v>31.65</v>
       </c>
-      <c r="AB3" s="47">
+      <c r="AB3" s="34">
         <v>0.6</v>
       </c>
-      <c r="AC3" s="48">
+      <c r="AC3" s="35">
         <v>0.4</v>
       </c>
-      <c r="AD3" s="44" t="str">
+      <c r="AD3" s="31" t="str">
         <f>CONCATENATE("stat(bullet_velocity;",'545-ammo'!$AE3,";",'545-ammo'!$AF3,";",'545-ammo'!$AG3,";",'545-ammo'!$AH3,")")</f>
         <v>stat(bullet_velocity;0;0.4;500;2000)</v>
       </c>
-      <c r="AE3" s="47">
-        <v>0.0</v>
-      </c>
-      <c r="AF3" s="47">
+      <c r="AE3" s="34">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="34">
         <v>0.4</v>
       </c>
-      <c r="AG3" s="49">
-        <v>500.0</v>
-      </c>
-      <c r="AH3" s="49">
-        <v>2000.0</v>
-      </c>
-      <c r="AI3" s="50">
+      <c r="AG3" s="36">
+        <v>500</v>
+      </c>
+      <c r="AH3" s="36">
+        <v>2000</v>
+      </c>
+      <c r="AI3" s="37">
         <f>Model!$B$4+IF(I3="",0,I3)</f>
         <v>1139.02</v>
       </c>
-      <c r="AJ3" s="46">
-        <f t="shared" ref="AJ3:AJ13" si="1">MAX(AE3,MIN(AF3,AE3+(AI3-AG3)*(AF3-AE3)/(AH3-AG3)))</f>
-        <v>0.1704053333</v>
-      </c>
-      <c r="AK3" s="51">
-        <v>59.0</v>
-      </c>
-      <c r="AL3" s="52" t="s">
+      <c r="AJ3" s="33">
+        <f t="shared" ref="AJ3:AJ13" si="0">MAX(AE3,MIN(AF3,AE3+(AI3-AG3)*(AF3-AE3)/(AH3-AG3)))</f>
+        <v>0.17040533333333333</v>
+      </c>
+      <c r="AK3" s="38">
+        <v>59</v>
+      </c>
+      <c r="AL3" s="39" t="s">
         <v>86</v>
       </c>
-      <c r="AM3" s="53">
+      <c r="AM3" s="40">
         <f>C3*Model!$B$24+D3*Model!$B$25+E3*Model!$B$26+F3*Model!$B$27+G3*Model!$B$28+H3*Model!$B$29+I3*Model!$B$30+J3*Model!$B$31+K3*Model!$B$32+L3*Model!$B$33</f>
-        <v>0.0001</v>
-      </c>
-      <c r="AN3" s="53">
+        <v>1E-4</v>
+      </c>
+      <c r="AN3" s="40">
         <f>(AA3-Model!$B$5)*Model!$B$36</f>
-        <v>-2.52</v>
-      </c>
-      <c r="AO3" s="53">
+        <v>-2.5199999999999996</v>
+      </c>
+      <c r="AO3" s="40">
         <f>(Model!$B$6-AB3)*Model!$B$37</f>
         <v>0</v>
       </c>
-      <c r="AP3" s="53">
+      <c r="AP3" s="40">
         <f>(AC3-Model!$B$7)*Model!$B$38</f>
         <v>0</v>
       </c>
-      <c r="AQ3" s="53">
+      <c r="AQ3" s="40">
         <f>(AJ3-Model!$B$8)*Model!$B$39</f>
-        <v>0.08162133333</v>
-      </c>
-      <c r="AR3" s="53">
-        <f t="shared" ref="AR3:AR13" si="2">SUM(AM3:AQ3)</f>
-        <v>-2.438278667</v>
+        <v>8.1621333333333324E-2</v>
+      </c>
+      <c r="AR3" s="40">
+        <f t="shared" ref="AR3:AR13" si="1">SUM(AM3:AQ3)</f>
+        <v>-2.4382786666666663</v>
       </c>
     </row>
-    <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="37" t="s">
+    <row r="4" spans="1:44" ht="14.25" customHeight="1">
+      <c r="A4" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="B4" s="37" t="s">
+      <c r="B4" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="C4" s="38">
-        <v>2.0</v>
-      </c>
-      <c r="D4" s="39">
+      <c r="C4" s="26">
+        <v>2</v>
+      </c>
+      <c r="D4" s="27">
         <v>0.01</v>
       </c>
-      <c r="E4" s="54">
-        <v>-1.0</v>
-      </c>
-      <c r="F4" s="54">
-        <v>-1.0</v>
-      </c>
-      <c r="G4" s="39">
+      <c r="E4" s="41">
+        <v>-1</v>
+      </c>
+      <c r="F4" s="41">
+        <v>-1</v>
+      </c>
+      <c r="G4" s="27">
         <v>0.1</v>
       </c>
-      <c r="H4" s="41"/>
-      <c r="I4" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="J4" s="40"/>
-      <c r="K4" s="42"/>
-      <c r="L4" s="55">
-        <v>500.0</v>
-      </c>
-      <c r="M4" s="43">
-        <v>-0.074</v>
-      </c>
-      <c r="N4" s="43">
-        <v>39.0</v>
-      </c>
-      <c r="O4" s="43">
+      <c r="H4" s="29"/>
+      <c r="I4" s="41">
+        <v>0</v>
+      </c>
+      <c r="J4" s="28"/>
+      <c r="K4" s="30"/>
+      <c r="L4" s="42">
+        <v>500</v>
+      </c>
+      <c r="M4" s="31">
+        <v>-7.3999999999999996E-2</v>
+      </c>
+      <c r="N4" s="31">
+        <v>39</v>
+      </c>
+      <c r="O4" s="31">
         <v>38.5</v>
       </c>
-      <c r="P4" s="43">
-        <v>1.0</v>
-      </c>
-      <c r="Q4" s="44">
+      <c r="P4" s="31">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="31">
         <v>0.3</v>
       </c>
-      <c r="R4" s="44">
+      <c r="R4" s="31">
         <v>0.5</v>
       </c>
-      <c r="S4" s="44">
-        <v>3.0</v>
-      </c>
-      <c r="T4" s="46">
+      <c r="S4" s="31">
+        <v>3</v>
+      </c>
+      <c r="T4" s="33">
         <f>MAX(MIN($M4*Model!$A$13+$N4,$O4)*$P4,0)</f>
         <v>37.15</v>
       </c>
-      <c r="U4" s="46">
+      <c r="U4" s="33">
         <f>MAX(MIN($M4*Model!$A$14+$N4,$O4)*$P4,0)</f>
-        <v>33.45</v>
-      </c>
-      <c r="V4" s="46">
+        <v>33.450000000000003</v>
+      </c>
+      <c r="V4" s="33">
         <f>MAX(MIN($M4*Model!$A$15+$N4,$O4)*$P4,0)</f>
         <v>27.9</v>
       </c>
-      <c r="W4" s="46">
+      <c r="W4" s="33">
         <f>MAX(MIN($M4*Model!$A$16+$N4,$O4)*$P4,0)</f>
         <v>20.5</v>
       </c>
-      <c r="X4" s="46">
+      <c r="X4" s="33">
         <f>MAX(MIN($M4*Model!$A$17+$N4,$O4)*$P4,0)</f>
         <v>38.5</v>
       </c>
-      <c r="Y4" s="46">
+      <c r="Y4" s="33">
         <f>MAX(MIN($M4*Model!$A$18+$N4,$O4)*$P4,0)</f>
         <v>38.5</v>
       </c>
-      <c r="Z4" s="46">
+      <c r="Z4" s="33">
         <f>MAX(MIN($M4*Model!$A$19+$N4,$O4)*$P4,0)</f>
         <v>38.5</v>
       </c>
-      <c r="AA4" s="46">
+      <c r="AA4" s="33">
         <f>T4*Model!$B$13+U4*Model!$B$14+V4*Model!$B$15+W4*Model!$B$16+X4*Model!$B$17+Y4*Model!$B$18+Z4*Model!$B$19</f>
         <v>31.23</v>
       </c>
-      <c r="AB4" s="47">
+      <c r="AB4" s="34">
         <v>0.65</v>
       </c>
-      <c r="AC4" s="47">
+      <c r="AC4" s="34">
         <v>0.6</v>
       </c>
-      <c r="AD4" s="44" t="str">
+      <c r="AD4" s="31" t="str">
         <f>CONCATENATE("stat(bullet_velocity;",'545-ammo'!$AE4,";",'545-ammo'!$AF4,";",'545-ammo'!$AG4,";",'545-ammo'!$AH4,")")</f>
         <v>stat(bullet_velocity;0;0.3;500;2000)</v>
       </c>
-      <c r="AE4" s="47">
-        <v>0.0</v>
-      </c>
-      <c r="AF4" s="47">
+      <c r="AE4" s="34">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="34">
         <v>0.3</v>
       </c>
-      <c r="AG4" s="49">
-        <v>500.0</v>
-      </c>
-      <c r="AH4" s="49">
-        <v>2000.0</v>
-      </c>
-      <c r="AI4" s="50">
+      <c r="AG4" s="36">
+        <v>500</v>
+      </c>
+      <c r="AH4" s="36">
+        <v>2000</v>
+      </c>
+      <c r="AI4" s="37">
         <f>Model!$B$4+IF(I4="",0,I4)</f>
         <v>1139</v>
       </c>
-      <c r="AJ4" s="46">
+      <c r="AJ4" s="33">
+        <f t="shared" si="0"/>
+        <v>0.1278</v>
+      </c>
+      <c r="AK4" s="38">
+        <v>65</v>
+      </c>
+      <c r="AL4" s="39" t="s">
+        <v>86</v>
+      </c>
+      <c r="AM4" s="40">
+        <f>C4*Model!$B$24+D4*Model!$B$25+E4*Model!$B$26+F4*Model!$B$27+G4*Model!$B$28+H4*Model!$B$29+I4*Model!$B$30+J4*Model!$B$31+K4*Model!$B$32+L4*Model!$B$33</f>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AN4" s="40">
+        <f>(AA4-Model!$B$5)*Model!$B$36</f>
+        <v>-3.1499999999999968</v>
+      </c>
+      <c r="AO4" s="40">
+        <f>(Model!$B$6-AB4)*Model!$B$37</f>
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="AP4" s="40">
+        <f>(AC4-Model!$B$7)*Model!$B$38</f>
+        <v>0.59999999999999987</v>
+      </c>
+      <c r="AQ4" s="40">
+        <f>(AJ4-Model!$B$8)*Model!$B$39</f>
+        <v>-8.879999999999999E-2</v>
+      </c>
+      <c r="AR4" s="40">
         <f t="shared" si="1"/>
-        <v>0.1278</v>
-      </c>
-      <c r="AK4" s="51">
-        <v>65.0</v>
-      </c>
-      <c r="AL4" s="52" t="s">
-        <v>86</v>
-      </c>
-      <c r="AM4" s="53">
-        <f>C4*Model!$B$24+D4*Model!$B$25+E4*Model!$B$26+F4*Model!$B$27+G4*Model!$B$28+H4*Model!$B$29+I4*Model!$B$30+J4*Model!$B$31+K4*Model!$B$32+L4*Model!$B$33</f>
-        <v>2.2</v>
-      </c>
-      <c r="AN4" s="53">
-        <f>(AA4-Model!$B$5)*Model!$B$36</f>
-        <v>-3.15</v>
-      </c>
-      <c r="AO4" s="53">
-        <f>(Model!$B$6-AB4)*Model!$B$37</f>
+        <v>-0.33879999999999666</v>
+      </c>
+    </row>
+    <row r="5" spans="1:44" ht="14.25" customHeight="1">
+      <c r="A5" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="B5" s="43" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" s="44">
+        <v>-1</v>
+      </c>
+      <c r="D5" s="45">
+        <v>0</v>
+      </c>
+      <c r="E5" s="46">
+        <v>1</v>
+      </c>
+      <c r="F5" s="44">
+        <v>1</v>
+      </c>
+      <c r="G5" s="47">
         <v>-0.1</v>
       </c>
-      <c r="AP4" s="53">
-        <f>(AC4-Model!$B$7)*Model!$B$38</f>
-        <v>0.6</v>
-      </c>
-      <c r="AQ4" s="53">
-        <f>(AJ4-Model!$B$8)*Model!$B$39</f>
-        <v>-0.0888</v>
-      </c>
-      <c r="AR4" s="53">
-        <f t="shared" si="2"/>
-        <v>-0.5388</v>
-      </c>
-    </row>
-    <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="56" t="s">
-        <v>89</v>
-      </c>
-      <c r="B5" s="56" t="s">
-        <v>90</v>
-      </c>
-      <c r="C5" s="57">
-        <v>-1.0</v>
-      </c>
-      <c r="D5" s="58">
-        <v>0.0</v>
-      </c>
-      <c r="E5" s="59">
-        <v>1.0</v>
-      </c>
-      <c r="F5" s="57">
-        <v>1.0</v>
-      </c>
-      <c r="G5" s="60">
-        <v>-0.1</v>
-      </c>
-      <c r="H5" s="61"/>
-      <c r="I5" s="59">
-        <v>100.0</v>
-      </c>
-      <c r="J5" s="60"/>
-      <c r="K5" s="62"/>
-      <c r="L5" s="63">
-        <v>1000.0</v>
-      </c>
-      <c r="M5" s="64">
-        <v>-0.066</v>
-      </c>
-      <c r="N5" s="64">
+      <c r="H5" s="48"/>
+      <c r="I5" s="46">
+        <v>100</v>
+      </c>
+      <c r="J5" s="47"/>
+      <c r="K5" s="49"/>
+      <c r="L5" s="50">
+        <v>1000</v>
+      </c>
+      <c r="M5" s="51">
+        <v>-6.6000000000000003E-2</v>
+      </c>
+      <c r="N5" s="51">
         <v>39.5</v>
       </c>
-      <c r="O5" s="64">
+      <c r="O5" s="51">
         <v>38.5</v>
       </c>
-      <c r="P5" s="64">
-        <v>1.0</v>
-      </c>
-      <c r="Q5" s="44">
+      <c r="P5" s="51">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="31">
         <v>0.3</v>
       </c>
-      <c r="R5" s="44">
+      <c r="R5" s="31">
         <v>0.5</v>
       </c>
-      <c r="S5" s="44">
-        <v>3.0</v>
-      </c>
-      <c r="T5" s="65">
+      <c r="S5" s="31">
+        <v>3</v>
+      </c>
+      <c r="T5" s="52">
         <f>MAX(MIN($M5*Model!$A$13+$N5,$O5)*$P5,0)</f>
         <v>37.85</v>
       </c>
-      <c r="U5" s="65">
+      <c r="U5" s="52">
         <f>MAX(MIN($M5*Model!$A$14+$N5,$O5)*$P5,0)</f>
-        <v>34.55</v>
-      </c>
-      <c r="V5" s="65">
+        <v>34.549999999999997</v>
+      </c>
+      <c r="V5" s="52">
         <f>MAX(MIN($M5*Model!$A$15+$N5,$O5)*$P5,0)</f>
         <v>29.6</v>
       </c>
-      <c r="W5" s="65">
+      <c r="W5" s="52">
         <f>MAX(MIN($M5*Model!$A$16+$N5,$O5)*$P5,0)</f>
         <v>23</v>
       </c>
-      <c r="X5" s="65">
+      <c r="X5" s="52">
         <f>MAX(MIN($M5*Model!$A$17+$N5,$O5)*$P5,0)</f>
         <v>38.5</v>
       </c>
-      <c r="Y5" s="65">
+      <c r="Y5" s="52">
         <f>MAX(MIN($M5*Model!$A$18+$N5,$O5)*$P5,0)</f>
         <v>38.5</v>
       </c>
-      <c r="Z5" s="65">
+      <c r="Z5" s="52">
         <f>MAX(MIN($M5*Model!$A$19+$N5,$O5)*$P5,0)</f>
         <v>38.5</v>
       </c>
-      <c r="AA5" s="65">
+      <c r="AA5" s="52">
         <f>T5*Model!$B$13+U5*Model!$B$14+V5*Model!$B$15+W5*Model!$B$16+X5*Model!$B$17+Y5*Model!$B$18+Z5*Model!$B$19</f>
         <v>32.57</v>
       </c>
-      <c r="AB5" s="66">
+      <c r="AB5" s="53">
         <v>0.6</v>
       </c>
-      <c r="AC5" s="66">
+      <c r="AC5" s="53">
         <v>0.45</v>
       </c>
-      <c r="AD5" s="44" t="str">
+      <c r="AD5" s="31" t="str">
         <f>CONCATENATE("stat(bullet_velocity;",'545-ammo'!$AE5,";",'545-ammo'!$AF5,";",'545-ammo'!$AG5,";",'545-ammo'!$AH5,")")</f>
         <v>stat(bullet_velocity;0;0.4;500;2000)</v>
       </c>
-      <c r="AE5" s="66">
-        <v>0.0</v>
-      </c>
-      <c r="AF5" s="66">
+      <c r="AE5" s="53">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="53">
         <v>0.4</v>
       </c>
-      <c r="AG5" s="49">
-        <v>500.0</v>
-      </c>
-      <c r="AH5" s="49">
-        <v>2000.0</v>
-      </c>
-      <c r="AI5" s="67">
+      <c r="AG5" s="36">
+        <v>500</v>
+      </c>
+      <c r="AH5" s="36">
+        <v>2000</v>
+      </c>
+      <c r="AI5" s="54">
         <f>Model!$B$4+IF(I5="",0,I5)</f>
         <v>1239</v>
       </c>
-      <c r="AJ5" s="65">
-        <f t="shared" si="1"/>
-        <v>0.1970666667</v>
-      </c>
-      <c r="AK5" s="68">
-        <v>69.0</v>
-      </c>
-      <c r="AL5" s="69" t="s">
+      <c r="AJ5" s="52">
+        <f t="shared" si="0"/>
+        <v>0.1970666666666667</v>
+      </c>
+      <c r="AK5" s="55">
+        <v>69</v>
+      </c>
+      <c r="AL5" s="56" t="s">
         <v>86</v>
       </c>
-      <c r="AM5" s="53">
+      <c r="AM5" s="40">
         <f>C5*Model!$B$24+D5*Model!$B$25+E5*Model!$B$26+F5*Model!$B$27+G5*Model!$B$28+H5*Model!$B$29+I5*Model!$B$30+J5*Model!$B$31+K5*Model!$B$32+L5*Model!$B$33</f>
-        <v>-0.9</v>
-      </c>
-      <c r="AN5" s="70">
+        <v>-0.89999999999999991</v>
+      </c>
+      <c r="AN5" s="57">
         <f>(AA5-Model!$B$5)*Model!$B$36</f>
-        <v>-1.14</v>
-      </c>
-      <c r="AO5" s="70">
+        <v>-1.139999999999997</v>
+      </c>
+      <c r="AO5" s="57">
         <f>(Model!$B$6-AB5)*Model!$B$37</f>
         <v>0</v>
       </c>
-      <c r="AP5" s="70">
+      <c r="AP5" s="57">
         <f>(AC5-Model!$B$7)*Model!$B$38</f>
-        <v>0.15</v>
-      </c>
-      <c r="AQ5" s="70">
+        <v>0.14999999999999997</v>
+      </c>
+      <c r="AQ5" s="57">
         <f>(AJ5-Model!$B$8)*Model!$B$39</f>
-        <v>0.1882666667</v>
-      </c>
-      <c r="AR5" s="70">
-        <f t="shared" si="2"/>
-        <v>-1.701733333</v>
+        <v>0.1882666666666668</v>
+      </c>
+      <c r="AR5" s="57">
+        <f t="shared" si="1"/>
+        <v>-1.7017333333333302</v>
       </c>
     </row>
-    <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="37" t="s">
+    <row r="6" spans="1:44" ht="14.25" customHeight="1">
+      <c r="A6" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="C6" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="D6" s="39">
+      <c r="C6" s="41">
+        <v>0</v>
+      </c>
+      <c r="D6" s="27">
         <v>0.02</v>
       </c>
-      <c r="E6" s="38">
-        <v>2.0</v>
-      </c>
-      <c r="F6" s="54">
-        <v>1.0</v>
-      </c>
-      <c r="G6" s="40">
+      <c r="E6" s="26">
+        <v>2</v>
+      </c>
+      <c r="F6" s="41">
+        <v>1</v>
+      </c>
+      <c r="G6" s="28">
         <v>-0.05</v>
       </c>
-      <c r="H6" s="41"/>
-      <c r="I6" s="38">
-        <v>50.0</v>
-      </c>
-      <c r="J6" s="40"/>
-      <c r="K6" s="42"/>
-      <c r="L6" s="42">
-        <v>1250.0</v>
-      </c>
-      <c r="M6" s="43">
-        <v>-0.074</v>
-      </c>
-      <c r="N6" s="43">
-        <v>41.0</v>
-      </c>
-      <c r="O6" s="43">
+      <c r="H6" s="29"/>
+      <c r="I6" s="26">
+        <v>50</v>
+      </c>
+      <c r="J6" s="28"/>
+      <c r="K6" s="30"/>
+      <c r="L6" s="30">
+        <v>1250</v>
+      </c>
+      <c r="M6" s="31">
+        <v>-7.3999999999999996E-2</v>
+      </c>
+      <c r="N6" s="31">
+        <v>41</v>
+      </c>
+      <c r="O6" s="31">
         <v>39.5</v>
       </c>
-      <c r="P6" s="43">
-        <v>1.0</v>
-      </c>
-      <c r="Q6" s="44">
+      <c r="P6" s="31">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="31">
         <v>0.3</v>
       </c>
-      <c r="R6" s="44">
+      <c r="R6" s="31">
         <v>0.5</v>
       </c>
-      <c r="S6" s="44">
-        <v>3.0</v>
-      </c>
-      <c r="T6" s="46">
+      <c r="S6" s="31">
+        <v>3</v>
+      </c>
+      <c r="T6" s="33">
         <f>MAX(MIN($M6*Model!$A$13+$N6,$O6)*$P6,0)</f>
         <v>39.15</v>
       </c>
-      <c r="U6" s="46">
+      <c r="U6" s="33">
         <f>MAX(MIN($M6*Model!$A$14+$N6,$O6)*$P6,0)</f>
-        <v>35.45</v>
-      </c>
-      <c r="V6" s="46">
+        <v>35.450000000000003</v>
+      </c>
+      <c r="V6" s="33">
         <f>MAX(MIN($M6*Model!$A$15+$N6,$O6)*$P6,0)</f>
         <v>29.9</v>
       </c>
-      <c r="W6" s="46">
+      <c r="W6" s="33">
         <f>MAX(MIN($M6*Model!$A$16+$N6,$O6)*$P6,0)</f>
         <v>22.5</v>
       </c>
-      <c r="X6" s="46">
+      <c r="X6" s="33">
         <f>MAX(MIN($M6*Model!$A$17+$N6,$O6)*$P6,0)</f>
         <v>39.5</v>
       </c>
-      <c r="Y6" s="46">
+      <c r="Y6" s="33">
         <f>MAX(MIN($M6*Model!$A$18+$N6,$O6)*$P6,0)</f>
         <v>39.5</v>
       </c>
-      <c r="Z6" s="46">
+      <c r="Z6" s="33">
         <f>MAX(MIN($M6*Model!$A$19+$N6,$O6)*$P6,0)</f>
         <v>39.5</v>
       </c>
-      <c r="AA6" s="46">
+      <c r="AA6" s="33">
         <f>T6*Model!$B$13+U6*Model!$B$14+V6*Model!$B$15+W6*Model!$B$16+X6*Model!$B$17+Y6*Model!$B$18+Z6*Model!$B$19</f>
-        <v>33.23</v>
-      </c>
-      <c r="AB6" s="47">
+        <v>33.229999999999997</v>
+      </c>
+      <c r="AB6" s="34">
         <v>0.5</v>
       </c>
-      <c r="AC6" s="47">
+      <c r="AC6" s="34">
         <v>0.45</v>
       </c>
-      <c r="AD6" s="44" t="str">
+      <c r="AD6" s="31" t="str">
         <f>CONCATENATE("stat(bullet_velocity;",'545-ammo'!$AE6,";",'545-ammo'!$AF6,";",'545-ammo'!$AG6,";",'545-ammo'!$AH6,")")</f>
         <v>stat(bullet_velocity;0;0.5;500;2000)</v>
       </c>
-      <c r="AE6" s="47">
-        <v>0.0</v>
-      </c>
-      <c r="AF6" s="47">
+      <c r="AE6" s="34">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="34">
         <v>0.5</v>
       </c>
-      <c r="AG6" s="49">
-        <v>500.0</v>
-      </c>
-      <c r="AH6" s="49">
-        <v>2000.0</v>
-      </c>
-      <c r="AI6" s="50">
+      <c r="AG6" s="36">
+        <v>500</v>
+      </c>
+      <c r="AH6" s="36">
+        <v>2000</v>
+      </c>
+      <c r="AI6" s="37">
         <f>Model!$B$4+IF(I6="",0,I6)</f>
         <v>1189</v>
       </c>
-      <c r="AJ6" s="46">
-        <f t="shared" si="1"/>
-        <v>0.2296666667</v>
-      </c>
-      <c r="AK6" s="51">
-        <v>62.0</v>
-      </c>
-      <c r="AL6" s="52" t="s">
+      <c r="AJ6" s="33">
+        <f t="shared" si="0"/>
+        <v>0.22966666666666666</v>
+      </c>
+      <c r="AK6" s="38">
+        <v>62</v>
+      </c>
+      <c r="AL6" s="39" t="s">
         <v>86</v>
       </c>
-      <c r="AM6" s="53">
+      <c r="AM6" s="40">
         <f>C6*Model!$B$24+D6*Model!$B$25+E6*Model!$B$26+F6*Model!$B$27+G6*Model!$B$28+H6*Model!$B$29+I6*Model!$B$30+J6*Model!$B$31+K6*Model!$B$32+L6*Model!$B$33</f>
         <v>-1.85</v>
       </c>
-      <c r="AN6" s="53">
+      <c r="AN6" s="40">
         <f>(AA6-Model!$B$5)*Model!$B$36</f>
-        <v>-0.15</v>
-      </c>
-      <c r="AO6" s="53">
+        <v>-0.15000000000000213</v>
+      </c>
+      <c r="AO6" s="40">
         <f>(Model!$B$6-AB6)*Model!$B$37</f>
-        <v>0.2</v>
-      </c>
-      <c r="AP6" s="53">
+        <v>-0.19999999999999996</v>
+      </c>
+      <c r="AP6" s="40">
         <f>(AC6-Model!$B$7)*Model!$B$38</f>
-        <v>0.15</v>
-      </c>
-      <c r="AQ6" s="53">
+        <v>0.14999999999999997</v>
+      </c>
+      <c r="AQ6" s="40">
         <f>(AJ6-Model!$B$8)*Model!$B$39</f>
-        <v>0.3186666667</v>
-      </c>
-      <c r="AR6" s="53">
-        <f t="shared" si="2"/>
-        <v>-1.331333333</v>
+        <v>0.31866666666666665</v>
+      </c>
+      <c r="AR6" s="40">
+        <f t="shared" si="1"/>
+        <v>-1.7313333333333354</v>
       </c>
     </row>
-    <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="37" t="s">
+    <row r="7" spans="1:44" ht="14.25" customHeight="1">
+      <c r="A7" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="C7" s="54">
-        <v>-2.0</v>
-      </c>
-      <c r="D7" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="E7" s="38">
-        <v>3.0</v>
-      </c>
-      <c r="F7" s="38">
-        <v>2.0</v>
-      </c>
-      <c r="G7" s="39">
+      <c r="C7" s="41">
+        <v>-2</v>
+      </c>
+      <c r="D7" s="27">
+        <v>0</v>
+      </c>
+      <c r="E7" s="26">
+        <v>3</v>
+      </c>
+      <c r="F7" s="26">
+        <v>2</v>
+      </c>
+      <c r="G7" s="27">
         <v>-0.2</v>
       </c>
-      <c r="H7" s="41"/>
-      <c r="I7" s="38">
-        <v>200.0</v>
-      </c>
-      <c r="J7" s="40"/>
-      <c r="K7" s="42"/>
-      <c r="L7" s="55">
-        <v>3000.0</v>
-      </c>
-      <c r="M7" s="43">
-        <v>-0.064</v>
-      </c>
-      <c r="N7" s="43">
-        <v>41.0</v>
-      </c>
-      <c r="O7" s="43">
-        <v>40.0</v>
-      </c>
-      <c r="P7" s="43">
-        <v>1.0</v>
-      </c>
-      <c r="Q7" s="44">
+      <c r="H7" s="29"/>
+      <c r="I7" s="26">
+        <v>200</v>
+      </c>
+      <c r="J7" s="28"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="42">
+        <v>3000</v>
+      </c>
+      <c r="M7" s="31">
+        <v>-6.4000000000000001E-2</v>
+      </c>
+      <c r="N7" s="31">
+        <v>41</v>
+      </c>
+      <c r="O7" s="31">
+        <v>40</v>
+      </c>
+      <c r="P7" s="31">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="31">
         <v>0.3</v>
       </c>
-      <c r="R7" s="44">
+      <c r="R7" s="31">
         <v>0.5</v>
       </c>
-      <c r="S7" s="44">
-        <v>3.0</v>
-      </c>
-      <c r="T7" s="46">
+      <c r="S7" s="31">
+        <v>3</v>
+      </c>
+      <c r="T7" s="33">
         <f>MAX(MIN($M7*Model!$A$13+$N7,$O7)*$P7,0)</f>
         <v>39.4</v>
       </c>
-      <c r="U7" s="46">
+      <c r="U7" s="33">
         <f>MAX(MIN($M7*Model!$A$14+$N7,$O7)*$P7,0)</f>
-        <v>36.2</v>
-      </c>
-      <c r="V7" s="46">
+        <v>36.200000000000003</v>
+      </c>
+      <c r="V7" s="33">
         <f>MAX(MIN($M7*Model!$A$15+$N7,$O7)*$P7,0)</f>
         <v>31.4</v>
       </c>
-      <c r="W7" s="46">
+      <c r="W7" s="33">
         <f>MAX(MIN($M7*Model!$A$16+$N7,$O7)*$P7,0)</f>
         <v>25</v>
       </c>
-      <c r="X7" s="46">
+      <c r="X7" s="33">
         <f>MAX(MIN($M7*Model!$A$17+$N7,$O7)*$P7,0)</f>
         <v>40</v>
       </c>
-      <c r="Y7" s="46">
+      <c r="Y7" s="33">
         <f>MAX(MIN($M7*Model!$A$18+$N7,$O7)*$P7,0)</f>
         <v>40</v>
       </c>
-      <c r="Z7" s="46">
+      <c r="Z7" s="33">
         <f>MAX(MIN($M7*Model!$A$19+$N7,$O7)*$P7,0)</f>
         <v>40</v>
       </c>
-      <c r="AA7" s="46">
+      <c r="AA7" s="33">
         <f>T7*Model!$B$13+U7*Model!$B$14+V7*Model!$B$15+W7*Model!$B$16+X7*Model!$B$17+Y7*Model!$B$18+Z7*Model!$B$19</f>
         <v>34.28</v>
       </c>
-      <c r="AB7" s="47">
+      <c r="AB7" s="34">
         <v>0.7</v>
       </c>
-      <c r="AC7" s="47">
+      <c r="AC7" s="34">
         <v>0.5</v>
       </c>
-      <c r="AD7" s="44" t="str">
+      <c r="AD7" s="31" t="str">
         <f>CONCATENATE("stat(bullet_velocity;",'545-ammo'!$AE7,";",'545-ammo'!$AF7,";",'545-ammo'!$AG7,";",'545-ammo'!$AH7,")")</f>
         <v>stat(bullet_velocity;0.05;0.55;500;2000)</v>
       </c>
-      <c r="AE7" s="47">
+      <c r="AE7" s="34">
         <v>0.05</v>
       </c>
-      <c r="AF7" s="47">
-        <v>0.55</v>
-      </c>
-      <c r="AG7" s="49">
-        <v>500.0</v>
-      </c>
-      <c r="AH7" s="49">
-        <v>2000.0</v>
-      </c>
-      <c r="AI7" s="50">
+      <c r="AF7" s="34">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="AG7" s="36">
+        <v>500</v>
+      </c>
+      <c r="AH7" s="36">
+        <v>2000</v>
+      </c>
+      <c r="AI7" s="37">
         <f>Model!$B$4+IF(I7="",0,I7)</f>
         <v>1339</v>
       </c>
-      <c r="AJ7" s="46">
+      <c r="AJ7" s="33">
+        <f t="shared" si="0"/>
+        <v>0.32966666666666666</v>
+      </c>
+      <c r="AK7" s="38">
+        <v>63</v>
+      </c>
+      <c r="AL7" s="39" t="s">
+        <v>86</v>
+      </c>
+      <c r="AM7" s="40">
+        <f>C7*Model!$B$24+D7*Model!$B$25+E7*Model!$B$26+F7*Model!$B$27+G7*Model!$B$28+H7*Model!$B$29+I7*Model!$B$30+J7*Model!$B$31+K7*Model!$B$32+L7*Model!$B$33</f>
+        <v>-2.6000000000000005</v>
+      </c>
+      <c r="AN7" s="40">
+        <f>(AA7-Model!$B$5)*Model!$B$36</f>
+        <v>1.4250000000000043</v>
+      </c>
+      <c r="AO7" s="40">
+        <f>(Model!$B$6-AB7)*Model!$B$37</f>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AP7" s="40">
+        <f>(AC7-Model!$B$7)*Model!$B$38</f>
+        <v>0.29999999999999993</v>
+      </c>
+      <c r="AQ7" s="40">
+        <f>(AJ7-Model!$B$8)*Model!$B$39</f>
+        <v>0.71866666666666668</v>
+      </c>
+      <c r="AR7" s="40">
         <f t="shared" si="1"/>
-        <v>0.3296666667</v>
-      </c>
-      <c r="AK7" s="51">
-        <v>63.0</v>
-      </c>
-      <c r="AL7" s="52" t="s">
-        <v>86</v>
-      </c>
-      <c r="AM7" s="53">
-        <f>C7*Model!$B$24+D7*Model!$B$25+E7*Model!$B$26+F7*Model!$B$27+G7*Model!$B$28+H7*Model!$B$29+I7*Model!$B$30+J7*Model!$B$31+K7*Model!$B$32+L7*Model!$B$33</f>
-        <v>-2.6</v>
-      </c>
-      <c r="AN7" s="53">
-        <f>(AA7-Model!$B$5)*Model!$B$36</f>
-        <v>1.425</v>
-      </c>
-      <c r="AO7" s="53">
-        <f>(Model!$B$6-AB7)*Model!$B$37</f>
+        <v>4.3666666666670295E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:44" ht="14.25" customHeight="1">
+      <c r="A8" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" s="41">
+        <v>-1</v>
+      </c>
+      <c r="D8" s="27">
+        <v>0.08</v>
+      </c>
+      <c r="E8" s="41">
+        <v>2</v>
+      </c>
+      <c r="F8" s="41">
+        <v>3</v>
+      </c>
+      <c r="G8" s="27">
+        <v>-0.1</v>
+      </c>
+      <c r="H8" s="29"/>
+      <c r="I8" s="41">
+        <v>-100</v>
+      </c>
+      <c r="J8" s="28"/>
+      <c r="K8" s="42">
         <v>-0.2</v>
       </c>
-      <c r="AP7" s="53">
-        <f>(AC7-Model!$B$7)*Model!$B$38</f>
-        <v>0.3</v>
-      </c>
-      <c r="AQ7" s="53">
-        <f>(AJ7-Model!$B$8)*Model!$B$39</f>
-        <v>0.7186666667</v>
-      </c>
-      <c r="AR7" s="53">
-        <f t="shared" si="2"/>
-        <v>-0.3563333333</v>
-      </c>
-    </row>
-    <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="B8" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="C8" s="54">
-        <v>-1.0</v>
-      </c>
-      <c r="D8" s="39">
-        <v>0.08</v>
-      </c>
-      <c r="E8" s="54">
-        <v>2.0</v>
-      </c>
-      <c r="F8" s="54">
-        <v>3.0</v>
-      </c>
-      <c r="G8" s="39">
-        <v>-0.1</v>
-      </c>
-      <c r="H8" s="41"/>
-      <c r="I8" s="54">
-        <v>-100.0</v>
-      </c>
-      <c r="J8" s="40"/>
-      <c r="K8" s="55">
-        <v>-0.2</v>
-      </c>
-      <c r="L8" s="55">
-        <v>3500.0</v>
-      </c>
-      <c r="M8" s="43">
-        <v>-0.084</v>
-      </c>
-      <c r="N8" s="43">
-        <v>43.0</v>
-      </c>
-      <c r="O8" s="43">
-        <v>43.0</v>
-      </c>
-      <c r="P8" s="43">
-        <v>1.0</v>
-      </c>
-      <c r="Q8" s="44">
+      <c r="L8" s="42">
+        <v>3500</v>
+      </c>
+      <c r="M8" s="31">
+        <v>-8.4000000000000005E-2</v>
+      </c>
+      <c r="N8" s="31">
+        <v>43</v>
+      </c>
+      <c r="O8" s="31">
+        <v>43</v>
+      </c>
+      <c r="P8" s="31">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="31">
         <v>0.4</v>
       </c>
-      <c r="R8" s="45">
+      <c r="R8" s="32">
         <v>0.6</v>
       </c>
-      <c r="S8" s="44">
-        <v>3.0</v>
-      </c>
-      <c r="T8" s="46">
+      <c r="S8" s="31">
+        <v>3</v>
+      </c>
+      <c r="T8" s="33">
         <f>MAX(MIN($M8*Model!$A$13+$N8,$O8)*$P8,0)</f>
         <v>40.9</v>
       </c>
-      <c r="U8" s="46">
+      <c r="U8" s="33">
         <f>MAX(MIN($M8*Model!$A$14+$N8,$O8)*$P8,0)</f>
-        <v>36.7</v>
-      </c>
-      <c r="V8" s="46">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="V8" s="33">
         <f>MAX(MIN($M8*Model!$A$15+$N8,$O8)*$P8,0)</f>
         <v>30.4</v>
       </c>
-      <c r="W8" s="46">
+      <c r="W8" s="33">
         <f>MAX(MIN($M8*Model!$A$16+$N8,$O8)*$P8,0)</f>
         <v>22</v>
       </c>
-      <c r="X8" s="46">
+      <c r="X8" s="33">
         <f>MAX(MIN($M8*Model!$A$17+$N8,$O8)*$P8,0)</f>
         <v>43</v>
       </c>
-      <c r="Y8" s="46">
+      <c r="Y8" s="33">
         <f>MAX(MIN($M8*Model!$A$18+$N8,$O8)*$P8,0)</f>
         <v>43</v>
       </c>
-      <c r="Z8" s="46">
+      <c r="Z8" s="33">
         <f>MAX(MIN($M8*Model!$A$19+$N8,$O8)*$P8,0)</f>
         <v>43</v>
       </c>
-      <c r="AA8" s="46">
+      <c r="AA8" s="33">
         <f>T8*Model!$B$13+U8*Model!$B$14+V8*Model!$B$15+W8*Model!$B$16+X8*Model!$B$17+Y8*Model!$B$18+Z8*Model!$B$19</f>
         <v>34.18</v>
       </c>
-      <c r="AB8" s="47">
-        <v>0.55</v>
-      </c>
-      <c r="AC8" s="47">
+      <c r="AB8" s="34">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="AC8" s="34">
         <v>0.2</v>
       </c>
-      <c r="AD8" s="44" t="str">
+      <c r="AD8" s="31" t="str">
         <f>CONCATENATE("stat(bullet_velocity;",'545-ammo'!$AE8,";",'545-ammo'!$AF8,";",'545-ammo'!$AG8,";",'545-ammo'!$AH8,")")</f>
         <v>stat(bullet_velocity;0;0.25;500;2000)</v>
       </c>
-      <c r="AE8" s="47">
-        <v>0.0</v>
-      </c>
-      <c r="AF8" s="47">
+      <c r="AE8" s="34">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="34">
         <v>0.25</v>
       </c>
-      <c r="AG8" s="49">
-        <v>500.0</v>
-      </c>
-      <c r="AH8" s="49">
-        <v>2000.0</v>
-      </c>
-      <c r="AI8" s="50">
+      <c r="AG8" s="36">
+        <v>500</v>
+      </c>
+      <c r="AH8" s="36">
+        <v>2000</v>
+      </c>
+      <c r="AI8" s="37">
         <f>Model!$B$4+IF(I8="",0,I8)</f>
         <v>1039</v>
       </c>
-      <c r="AJ8" s="46">
-        <f t="shared" si="1"/>
-        <v>0.08983333333</v>
-      </c>
-      <c r="AK8" s="51">
-        <v>61.0</v>
-      </c>
-      <c r="AL8" s="52" t="s">
+      <c r="AJ8" s="33">
+        <f t="shared" si="0"/>
+        <v>8.9833333333333334E-2</v>
+      </c>
+      <c r="AK8" s="38">
+        <v>61</v>
+      </c>
+      <c r="AL8" s="39" t="s">
         <v>86</v>
       </c>
-      <c r="AM8" s="53">
+      <c r="AM8" s="40">
         <f>C8*Model!$B$24+D8*Model!$B$25+E8*Model!$B$26+F8*Model!$B$27+G8*Model!$B$28+H8*Model!$B$29+I8*Model!$B$30+J8*Model!$B$31+K8*Model!$B$32+L8*Model!$B$33</f>
         <v>-4.5</v>
       </c>
-      <c r="AN8" s="53">
+      <c r="AN8" s="40">
         <f>(AA8-Model!$B$5)*Model!$B$36</f>
-        <v>1.275</v>
-      </c>
-      <c r="AO8" s="53">
+        <v>1.2750000000000021</v>
+      </c>
+      <c r="AO8" s="40">
         <f>(Model!$B$6-AB8)*Model!$B$37</f>
-        <v>0.1</v>
-      </c>
-      <c r="AP8" s="53">
+        <v>-9.9999999999999867E-2</v>
+      </c>
+      <c r="AP8" s="40">
         <f>(AC8-Model!$B$7)*Model!$B$38</f>
-        <v>-0.6</v>
-      </c>
-      <c r="AQ8" s="53">
+        <v>-0.60000000000000009</v>
+      </c>
+      <c r="AQ8" s="40">
         <f>(AJ8-Model!$B$8)*Model!$B$39</f>
-        <v>-0.2406666667</v>
-      </c>
-      <c r="AR8" s="53">
-        <f t="shared" si="2"/>
-        <v>-3.965666667</v>
+        <v>-0.24066666666666664</v>
+      </c>
+      <c r="AR8" s="40">
+        <f t="shared" si="1"/>
+        <v>-4.165666666666664</v>
       </c>
     </row>
-    <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="37" t="s">
+    <row r="9" spans="1:44" ht="14.25" customHeight="1">
+      <c r="A9" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="B9" s="37" t="s">
+      <c r="B9" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="C9" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="D9" s="39">
+      <c r="C9" s="41">
+        <v>0</v>
+      </c>
+      <c r="D9" s="27">
         <v>-0.06</v>
       </c>
-      <c r="E9" s="54">
-        <v>-3.0</v>
-      </c>
-      <c r="F9" s="54">
-        <v>-2.0</v>
-      </c>
-      <c r="G9" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H9" s="41"/>
-      <c r="I9" s="54">
-        <v>100.0</v>
-      </c>
-      <c r="J9" s="40"/>
-      <c r="K9" s="42"/>
-      <c r="L9" s="55">
-        <v>750.0</v>
-      </c>
-      <c r="M9" s="43">
-        <v>-0.078</v>
-      </c>
-      <c r="N9" s="43">
+      <c r="E9" s="41">
+        <v>-3</v>
+      </c>
+      <c r="F9" s="41">
+        <v>-2</v>
+      </c>
+      <c r="G9" s="28">
+        <v>0</v>
+      </c>
+      <c r="H9" s="29"/>
+      <c r="I9" s="41">
+        <v>100</v>
+      </c>
+      <c r="J9" s="28"/>
+      <c r="K9" s="30"/>
+      <c r="L9" s="42">
+        <v>750</v>
+      </c>
+      <c r="M9" s="31">
+        <v>-7.8E-2</v>
+      </c>
+      <c r="N9" s="31">
         <v>38.5</v>
       </c>
-      <c r="O9" s="43">
-        <v>43.0</v>
-      </c>
-      <c r="P9" s="43">
-        <v>1.0</v>
-      </c>
-      <c r="Q9" s="44">
+      <c r="O9" s="31">
+        <v>43</v>
+      </c>
+      <c r="P9" s="31">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="31">
         <v>0.3</v>
       </c>
-      <c r="R9" s="44">
+      <c r="R9" s="31">
         <v>0.5</v>
       </c>
-      <c r="S9" s="44">
-        <v>3.0</v>
-      </c>
-      <c r="T9" s="46">
+      <c r="S9" s="31">
+        <v>3</v>
+      </c>
+      <c r="T9" s="33">
         <f>MAX(MIN($M9*Model!$A$13+$N9,$O9)*$P9,0)</f>
-        <v>36.55</v>
-      </c>
-      <c r="U9" s="46">
+        <v>36.549999999999997</v>
+      </c>
+      <c r="U9" s="33">
         <f>MAX(MIN($M9*Model!$A$14+$N9,$O9)*$P9,0)</f>
         <v>32.65</v>
       </c>
-      <c r="V9" s="46">
+      <c r="V9" s="33">
         <f>MAX(MIN($M9*Model!$A$15+$N9,$O9)*$P9,0)</f>
         <v>26.8</v>
       </c>
-      <c r="W9" s="46">
+      <c r="W9" s="33">
         <f>MAX(MIN($M9*Model!$A$16+$N9,$O9)*$P9,0)</f>
         <v>19</v>
       </c>
-      <c r="X9" s="46">
+      <c r="X9" s="33">
         <f>MAX(MIN($M9*Model!$A$17+$N9,$O9)*$P9,0)</f>
         <v>38.5</v>
       </c>
-      <c r="Y9" s="46">
+      <c r="Y9" s="33">
         <f>MAX(MIN($M9*Model!$A$18+$N9,$O9)*$P9,0)</f>
         <v>38.5</v>
       </c>
-      <c r="Z9" s="46">
+      <c r="Z9" s="33">
         <f>MAX(MIN($M9*Model!$A$19+$N9,$O9)*$P9,0)</f>
         <v>38.5</v>
       </c>
-      <c r="AA9" s="46">
+      <c r="AA9" s="33">
         <f>T9*Model!$B$13+U9*Model!$B$14+V9*Model!$B$15+W9*Model!$B$16+X9*Model!$B$17+Y9*Model!$B$18+Z9*Model!$B$19</f>
         <v>30.31</v>
       </c>
-      <c r="AB9" s="47">
+      <c r="AB9" s="34">
         <v>0.7</v>
       </c>
-      <c r="AC9" s="47">
+      <c r="AC9" s="34">
         <v>0.35</v>
       </c>
-      <c r="AD9" s="44" t="str">
+      <c r="AD9" s="31" t="str">
         <f>CONCATENATE("stat(bullet_velocity;",'545-ammo'!$AE9,";",'545-ammo'!$AF9,";",'545-ammo'!$AG9,";",'545-ammo'!$AH9,")")</f>
         <v>stat(bullet_velocity;0;0.05;500;2000)</v>
       </c>
-      <c r="AE9" s="48">
-        <v>0.0</v>
-      </c>
-      <c r="AF9" s="47">
+      <c r="AE9" s="35">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="34">
         <v>0.05</v>
       </c>
-      <c r="AG9" s="49">
-        <v>500.0</v>
-      </c>
-      <c r="AH9" s="49">
-        <v>2000.0</v>
-      </c>
-      <c r="AI9" s="50">
+      <c r="AG9" s="36">
+        <v>500</v>
+      </c>
+      <c r="AH9" s="36">
+        <v>2000</v>
+      </c>
+      <c r="AI9" s="37">
         <f>Model!$B$4+IF(I9="",0,I9)</f>
         <v>1239</v>
       </c>
-      <c r="AJ9" s="46">
+      <c r="AJ9" s="33">
+        <f t="shared" si="0"/>
+        <v>2.4633333333333337E-2</v>
+      </c>
+      <c r="AK9" s="38">
+        <v>60</v>
+      </c>
+      <c r="AL9" s="39" t="s">
+        <v>86</v>
+      </c>
+      <c r="AM9" s="40">
+        <f>C9*Model!$B$24+D9*Model!$B$25+E9*Model!$B$26+F9*Model!$B$27+G9*Model!$B$28+H9*Model!$B$29+I9*Model!$B$30+J9*Model!$B$31+K9*Model!$B$32+L9*Model!$B$33</f>
+        <v>5.3000000000000007</v>
+      </c>
+      <c r="AN9" s="40">
+        <f>(AA9-Model!$B$5)*Model!$B$36</f>
+        <v>-4.5299999999999994</v>
+      </c>
+      <c r="AO9" s="40">
+        <f>(Model!$B$6-AB9)*Model!$B$37</f>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AP9" s="40">
+        <f>(AC9-Model!$B$7)*Model!$B$38</f>
+        <v>-0.15000000000000013</v>
+      </c>
+      <c r="AQ9" s="40">
+        <f>(AJ9-Model!$B$8)*Model!$B$39</f>
+        <v>-0.50146666666666662</v>
+      </c>
+      <c r="AR9" s="40">
         <f t="shared" si="1"/>
-        <v>0.02463333333</v>
-      </c>
-      <c r="AK9" s="51">
-        <v>60.0</v>
-      </c>
-      <c r="AL9" s="52" t="s">
-        <v>86</v>
-      </c>
-      <c r="AM9" s="53">
-        <f>C9*Model!$B$24+D9*Model!$B$25+E9*Model!$B$26+F9*Model!$B$27+G9*Model!$B$28+H9*Model!$B$29+I9*Model!$B$30+J9*Model!$B$31+K9*Model!$B$32+L9*Model!$B$33</f>
-        <v>5.3</v>
-      </c>
-      <c r="AN9" s="53">
-        <f>(AA9-Model!$B$5)*Model!$B$36</f>
-        <v>-4.53</v>
-      </c>
-      <c r="AO9" s="53">
-        <f>(Model!$B$6-AB9)*Model!$B$37</f>
-        <v>-0.2</v>
-      </c>
-      <c r="AP9" s="53">
-        <f>(AC9-Model!$B$7)*Model!$B$38</f>
-        <v>-0.15</v>
-      </c>
-      <c r="AQ9" s="53">
-        <f>(AJ9-Model!$B$8)*Model!$B$39</f>
-        <v>-0.5014666667</v>
-      </c>
-      <c r="AR9" s="53">
-        <f t="shared" si="2"/>
-        <v>-0.08146666667</v>
+        <v>0.31853333333333456</v>
       </c>
     </row>
-    <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="37" t="s">
+    <row r="10" spans="1:44" ht="14.25" customHeight="1">
+      <c r="A10" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="B10" s="37" t="s">
+      <c r="B10" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="C10" s="54">
-        <v>3.0</v>
-      </c>
-      <c r="D10" s="39">
+      <c r="C10" s="41">
+        <v>3</v>
+      </c>
+      <c r="D10" s="27">
         <v>0.1</v>
       </c>
-      <c r="E10" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="F10" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="G10" s="39">
+      <c r="E10" s="41">
+        <v>0</v>
+      </c>
+      <c r="F10" s="41">
+        <v>0</v>
+      </c>
+      <c r="G10" s="27">
         <v>0.05</v>
       </c>
-      <c r="H10" s="41"/>
-      <c r="I10" s="54">
-        <v>-250.0</v>
-      </c>
-      <c r="J10" s="40"/>
-      <c r="K10" s="55">
-        <v>-0.7</v>
-      </c>
-      <c r="L10" s="55">
-        <v>2750.0</v>
-      </c>
-      <c r="M10" s="43">
+      <c r="H10" s="29"/>
+      <c r="I10" s="41">
+        <v>-250</v>
+      </c>
+      <c r="J10" s="28"/>
+      <c r="K10" s="42">
+        <v>-0.6</v>
+      </c>
+      <c r="L10" s="42">
+        <v>2750</v>
+      </c>
+      <c r="M10" s="31">
         <v>-0.108</v>
       </c>
-      <c r="N10" s="43">
+      <c r="N10" s="31">
         <v>42.5</v>
       </c>
-      <c r="O10" s="43">
-        <v>43.0</v>
-      </c>
-      <c r="P10" s="43">
-        <v>1.0</v>
-      </c>
-      <c r="Q10" s="44">
+      <c r="O10" s="31">
+        <v>43</v>
+      </c>
+      <c r="P10" s="31">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="31">
         <v>0.3</v>
       </c>
-      <c r="R10" s="44">
+      <c r="R10" s="31">
         <v>0.5</v>
       </c>
-      <c r="S10" s="44">
-        <v>3.0</v>
-      </c>
-      <c r="T10" s="46">
+      <c r="S10" s="31">
+        <v>3</v>
+      </c>
+      <c r="T10" s="33">
         <f>MAX(MIN($M10*Model!$A$13+$N10,$O10)*$P10,0)</f>
-        <v>39.8</v>
-      </c>
-      <c r="U10" s="46">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="U10" s="33">
         <f>MAX(MIN($M10*Model!$A$14+$N10,$O10)*$P10,0)</f>
         <v>34.4</v>
       </c>
-      <c r="V10" s="46">
+      <c r="V10" s="33">
         <f>MAX(MIN($M10*Model!$A$15+$N10,$O10)*$P10,0)</f>
         <v>26.3</v>
       </c>
-      <c r="W10" s="46">
+      <c r="W10" s="33">
         <f>MAX(MIN($M10*Model!$A$16+$N10,$O10)*$P10,0)</f>
         <v>15.5</v>
       </c>
-      <c r="X10" s="46">
+      <c r="X10" s="33">
         <f>MAX(MIN($M10*Model!$A$17+$N10,$O10)*$P10,0)</f>
         <v>42.5</v>
       </c>
-      <c r="Y10" s="46">
+      <c r="Y10" s="33">
         <f>MAX(MIN($M10*Model!$A$18+$N10,$O10)*$P10,0)</f>
         <v>42.5</v>
       </c>
-      <c r="Z10" s="46">
+      <c r="Z10" s="33">
         <f>MAX(MIN($M10*Model!$A$19+$N10,$O10)*$P10,0)</f>
         <v>42.5</v>
       </c>
-      <c r="AA10" s="46">
+      <c r="AA10" s="33">
         <f>T10*Model!$B$13+U10*Model!$B$14+V10*Model!$B$15+W10*Model!$B$16+X10*Model!$B$17+Y10*Model!$B$18+Z10*Model!$B$19</f>
-        <v>31.16</v>
-      </c>
-      <c r="AB10" s="47">
+        <v>31.159999999999997</v>
+      </c>
+      <c r="AB10" s="34">
         <v>0.6</v>
       </c>
-      <c r="AC10" s="48">
+      <c r="AC10" s="35">
         <v>0.1</v>
       </c>
-      <c r="AD10" s="44" t="str">
+      <c r="AD10" s="31" t="str">
         <f>CONCATENATE("stat(bullet_velocity;",'545-ammo'!$AE10,";",'545-ammo'!$AF10,";",'545-ammo'!$AG10,";",'545-ammo'!$AH10,")")</f>
         <v>stat(bullet_velocity;0;0.5;500;2000)</v>
       </c>
-      <c r="AE10" s="47">
-        <v>0.0</v>
-      </c>
-      <c r="AF10" s="47">
+      <c r="AE10" s="34">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="34">
         <v>0.5</v>
       </c>
-      <c r="AG10" s="49">
-        <v>500.0</v>
-      </c>
-      <c r="AH10" s="49">
-        <v>2000.0</v>
-      </c>
-      <c r="AI10" s="50">
+      <c r="AG10" s="36">
+        <v>500</v>
+      </c>
+      <c r="AH10" s="36">
+        <v>2000</v>
+      </c>
+      <c r="AI10" s="37">
         <f>Model!$B$4+IF(I10="",0,I10)</f>
         <v>889</v>
       </c>
-      <c r="AJ10" s="46">
-        <f t="shared" si="1"/>
-        <v>0.1296666667</v>
-      </c>
-      <c r="AK10" s="51">
-        <v>64.0</v>
-      </c>
-      <c r="AL10" s="52" t="s">
+      <c r="AJ10" s="33">
+        <f t="shared" si="0"/>
+        <v>0.12966666666666668</v>
+      </c>
+      <c r="AK10" s="38">
+        <v>64</v>
+      </c>
+      <c r="AL10" s="39" t="s">
         <v>86</v>
       </c>
-      <c r="AM10" s="53">
+      <c r="AM10" s="40">
         <f>C10*Model!$B$24+D10*Model!$B$25+E10*Model!$B$26+F10*Model!$B$27+G10*Model!$B$28+H10*Model!$B$29+I10*Model!$B$30+J10*Model!$B$31+K10*Model!$B$32+L10*Model!$B$33</f>
-        <v>2.75</v>
-      </c>
-      <c r="AN10" s="53">
+        <v>2.25</v>
+      </c>
+      <c r="AN10" s="40">
         <f>(AA10-Model!$B$5)*Model!$B$36</f>
-        <v>-3.255</v>
-      </c>
-      <c r="AO10" s="53">
+        <v>-3.2550000000000026</v>
+      </c>
+      <c r="AO10" s="40">
         <f>(Model!$B$6-AB10)*Model!$B$37</f>
         <v>0</v>
       </c>
-      <c r="AP10" s="53">
+      <c r="AP10" s="40">
         <f>(AC10-Model!$B$7)*Model!$B$38</f>
-        <v>-0.9</v>
-      </c>
-      <c r="AQ10" s="53">
+        <v>-0.90000000000000013</v>
+      </c>
+      <c r="AQ10" s="40">
         <f>(AJ10-Model!$B$8)*Model!$B$39</f>
-        <v>-0.08133333333</v>
-      </c>
-      <c r="AR10" s="53">
-        <f t="shared" si="2"/>
-        <v>-1.486333333</v>
+        <v>-8.1333333333333258E-2</v>
+      </c>
+      <c r="AR10" s="40">
+        <f t="shared" si="1"/>
+        <v>-1.9863333333333359</v>
       </c>
     </row>
-    <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="37" t="s">
+    <row r="11" spans="1:44" ht="14.25" customHeight="1">
+      <c r="A11" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="B11" s="37" t="s">
+      <c r="B11" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="54">
-        <v>1.0</v>
-      </c>
-      <c r="D11" s="39">
+      <c r="C11" s="41">
+        <v>1</v>
+      </c>
+      <c r="D11" s="27">
         <v>-0.06</v>
       </c>
-      <c r="E11" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="F11" s="54">
-        <v>-2.0</v>
-      </c>
-      <c r="G11" s="40">
+      <c r="E11" s="41">
+        <v>0</v>
+      </c>
+      <c r="F11" s="41">
+        <v>-2</v>
+      </c>
+      <c r="G11" s="28">
         <v>0.05</v>
       </c>
-      <c r="H11" s="41"/>
-      <c r="I11" s="38">
-        <v>100.0</v>
-      </c>
-      <c r="J11" s="40"/>
-      <c r="K11" s="42"/>
-      <c r="L11" s="42">
-        <v>1500.0</v>
-      </c>
-      <c r="M11" s="43">
-        <v>-0.088</v>
-      </c>
-      <c r="N11" s="43">
-        <v>41.0</v>
-      </c>
-      <c r="O11" s="43">
-        <v>42.0</v>
-      </c>
-      <c r="P11" s="43">
-        <v>1.0</v>
-      </c>
-      <c r="Q11" s="45">
+      <c r="H11" s="29"/>
+      <c r="I11" s="26">
+        <v>100</v>
+      </c>
+      <c r="J11" s="28"/>
+      <c r="K11" s="30"/>
+      <c r="L11" s="30">
+        <v>1500</v>
+      </c>
+      <c r="M11" s="31">
+        <v>-8.7999999999999995E-2</v>
+      </c>
+      <c r="N11" s="31">
+        <v>41</v>
+      </c>
+      <c r="O11" s="31">
+        <v>42</v>
+      </c>
+      <c r="P11" s="31">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="32">
         <v>0.45</v>
       </c>
-      <c r="R11" s="45">
+      <c r="R11" s="32">
         <v>0.65</v>
       </c>
-      <c r="S11" s="44">
-        <v>3.0</v>
-      </c>
-      <c r="T11" s="46">
+      <c r="S11" s="31">
+        <v>3</v>
+      </c>
+      <c r="T11" s="33">
         <f>MAX(MIN($M11*Model!$A$13+$N11,$O11)*$P11,0)</f>
-        <v>38.8</v>
-      </c>
-      <c r="U11" s="46">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="U11" s="33">
         <f>MAX(MIN($M11*Model!$A$14+$N11,$O11)*$P11,0)</f>
         <v>34.4</v>
       </c>
-      <c r="V11" s="46">
+      <c r="V11" s="33">
         <f>MAX(MIN($M11*Model!$A$15+$N11,$O11)*$P11,0)</f>
         <v>27.8</v>
       </c>
-      <c r="W11" s="46">
+      <c r="W11" s="33">
         <f>MAX(MIN($M11*Model!$A$16+$N11,$O11)*$P11,0)</f>
         <v>19</v>
       </c>
-      <c r="X11" s="46">
+      <c r="X11" s="33">
         <f>MAX(MIN($M11*Model!$A$17+$N11,$O11)*$P11,0)</f>
         <v>41</v>
       </c>
-      <c r="Y11" s="46">
+      <c r="Y11" s="33">
         <f>MAX(MIN($M11*Model!$A$18+$N11,$O11)*$P11,0)</f>
         <v>41</v>
       </c>
-      <c r="Z11" s="46">
+      <c r="Z11" s="33">
         <f>MAX(MIN($M11*Model!$A$19+$N11,$O11)*$P11,0)</f>
         <v>41</v>
       </c>
-      <c r="AA11" s="46">
+      <c r="AA11" s="33">
         <f>T11*Model!$B$13+U11*Model!$B$14+V11*Model!$B$15+W11*Model!$B$16+X11*Model!$B$17+Y11*Model!$B$18+Z11*Model!$B$19</f>
-        <v>31.76</v>
-      </c>
-      <c r="AB11" s="47">
+        <v>31.759999999999998</v>
+      </c>
+      <c r="AB11" s="34">
         <v>0.75</v>
       </c>
-      <c r="AC11" s="47">
+      <c r="AC11" s="34">
         <v>0.35</v>
       </c>
-      <c r="AD11" s="44" t="str">
+      <c r="AD11" s="31" t="str">
         <f>CONCATENATE("stat(bullet_velocity;",'545-ammo'!$AE11,";",'545-ammo'!$AF11,";",'545-ammo'!$AG11,";",'545-ammo'!$AH11,")")</f>
         <v>stat(bullet_velocity;0;0.15;500;2000)</v>
       </c>
-      <c r="AE11" s="47">
-        <v>0.0</v>
-      </c>
-      <c r="AF11" s="47">
+      <c r="AE11" s="34">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="34">
         <v>0.15</v>
       </c>
-      <c r="AG11" s="49">
-        <v>500.0</v>
-      </c>
-      <c r="AH11" s="49">
-        <v>2000.0</v>
-      </c>
-      <c r="AI11" s="50">
+      <c r="AG11" s="36">
+        <v>500</v>
+      </c>
+      <c r="AH11" s="36">
+        <v>2000</v>
+      </c>
+      <c r="AI11" s="37">
         <f>Model!$B$4+IF(I11="",0,I11)</f>
         <v>1239</v>
       </c>
-      <c r="AJ11" s="46">
-        <f t="shared" si="1"/>
-        <v>0.0739</v>
-      </c>
-      <c r="AK11" s="51">
-        <v>67.0</v>
-      </c>
-      <c r="AL11" s="52" t="s">
+      <c r="AJ11" s="33">
+        <f t="shared" si="0"/>
+        <v>7.3899999999999993E-2</v>
+      </c>
+      <c r="AK11" s="38">
+        <v>67</v>
+      </c>
+      <c r="AL11" s="39" t="s">
         <v>86</v>
       </c>
-      <c r="AM11" s="53">
+      <c r="AM11" s="40">
         <f>C11*Model!$B$24+D11*Model!$B$25+E11*Model!$B$26+F11*Model!$B$27+G11*Model!$B$28+H11*Model!$B$29+I11*Model!$B$30+J11*Model!$B$31+K11*Model!$B$32+L11*Model!$B$33</f>
-        <v>3.4</v>
-      </c>
-      <c r="AN11" s="53">
+        <v>3.4000000000000004</v>
+      </c>
+      <c r="AN11" s="40">
         <f>(AA11-Model!$B$5)*Model!$B$36</f>
-        <v>-2.355</v>
-      </c>
-      <c r="AO11" s="53">
+        <v>-2.3550000000000004</v>
+      </c>
+      <c r="AO11" s="40">
         <f>(Model!$B$6-AB11)*Model!$B$37</f>
-        <v>-0.3</v>
-      </c>
-      <c r="AP11" s="53">
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="AP11" s="40">
         <f>(AC11-Model!$B$7)*Model!$B$38</f>
-        <v>-0.15</v>
-      </c>
-      <c r="AQ11" s="53">
+        <v>-0.15000000000000013</v>
+      </c>
+      <c r="AQ11" s="40">
         <f>(AJ11-Model!$B$8)*Model!$B$39</f>
         <v>-0.3044</v>
       </c>
-      <c r="AR11" s="53">
-        <f t="shared" si="2"/>
-        <v>0.2906</v>
+      <c r="AR11" s="40">
+        <f t="shared" si="1"/>
+        <v>0.89059999999999984</v>
       </c>
     </row>
-    <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="37" t="s">
+    <row r="12" spans="1:44" ht="14.25" customHeight="1">
+      <c r="A12" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="B12" s="37" t="s">
+      <c r="B12" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="C12" s="38">
-        <v>-1.0</v>
-      </c>
-      <c r="D12" s="39">
+      <c r="C12" s="26">
+        <v>-1</v>
+      </c>
+      <c r="D12" s="27">
         <v>-0.09</v>
       </c>
-      <c r="E12" s="54">
-        <v>-1.0</v>
-      </c>
-      <c r="F12" s="38">
-        <v>-1.0</v>
-      </c>
-      <c r="G12" s="40">
+      <c r="E12" s="41">
+        <v>-1</v>
+      </c>
+      <c r="F12" s="26">
+        <v>-1</v>
+      </c>
+      <c r="G12" s="28">
         <v>-0.1</v>
       </c>
-      <c r="H12" s="41"/>
-      <c r="I12" s="38">
-        <v>300.0</v>
-      </c>
-      <c r="J12" s="40"/>
-      <c r="K12" s="42"/>
-      <c r="L12" s="42">
-        <v>2000.0</v>
-      </c>
-      <c r="M12" s="43">
-        <v>-0.062</v>
-      </c>
-      <c r="N12" s="43">
-        <v>37.0</v>
-      </c>
-      <c r="O12" s="43">
+      <c r="H12" s="29"/>
+      <c r="I12" s="26">
+        <v>300</v>
+      </c>
+      <c r="J12" s="28"/>
+      <c r="K12" s="30"/>
+      <c r="L12" s="30">
+        <v>2000</v>
+      </c>
+      <c r="M12" s="31">
+        <v>-6.2E-2</v>
+      </c>
+      <c r="N12" s="31">
+        <v>37</v>
+      </c>
+      <c r="O12" s="31">
         <v>36.5</v>
       </c>
-      <c r="P12" s="43">
-        <v>1.0</v>
-      </c>
-      <c r="Q12" s="44">
+      <c r="P12" s="31">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="31">
         <v>0.3</v>
       </c>
-      <c r="R12" s="44">
+      <c r="R12" s="31">
         <v>0.5</v>
       </c>
-      <c r="S12" s="44">
-        <v>3.0</v>
-      </c>
-      <c r="T12" s="46">
+      <c r="S12" s="31">
+        <v>3</v>
+      </c>
+      <c r="T12" s="33">
         <f>MAX(MIN($M12*Model!$A$13+$N12,$O12)*$P12,0)</f>
-        <v>35.45</v>
-      </c>
-      <c r="U12" s="46">
+        <v>35.450000000000003</v>
+      </c>
+      <c r="U12" s="33">
         <f>MAX(MIN($M12*Model!$A$14+$N12,$O12)*$P12,0)</f>
         <v>32.35</v>
       </c>
-      <c r="V12" s="46">
+      <c r="V12" s="33">
         <f>MAX(MIN($M12*Model!$A$15+$N12,$O12)*$P12,0)</f>
         <v>27.7</v>
       </c>
-      <c r="W12" s="46">
+      <c r="W12" s="33">
         <f>MAX(MIN($M12*Model!$A$16+$N12,$O12)*$P12,0)</f>
         <v>21.5</v>
       </c>
-      <c r="X12" s="46">
+      <c r="X12" s="33">
         <f>MAX(MIN($M12*Model!$A$17+$N12,$O12)*$P12,0)</f>
         <v>36.5</v>
       </c>
-      <c r="Y12" s="46">
+      <c r="Y12" s="33">
         <f>MAX(MIN($M12*Model!$A$18+$N12,$O12)*$P12,0)</f>
         <v>36.5</v>
       </c>
-      <c r="Z12" s="46">
+      <c r="Z12" s="33">
         <f>MAX(MIN($M12*Model!$A$19+$N12,$O12)*$P12,0)</f>
         <v>36.5</v>
       </c>
-      <c r="AA12" s="46">
+      <c r="AA12" s="33">
         <f>T12*Model!$B$13+U12*Model!$B$14+V12*Model!$B$15+W12*Model!$B$16+X12*Model!$B$17+Y12*Model!$B$18+Z12*Model!$B$19</f>
-        <v>30.49</v>
-      </c>
-      <c r="AB12" s="47">
+        <v>30.490000000000002</v>
+      </c>
+      <c r="AB12" s="34">
         <v>0.65</v>
       </c>
-      <c r="AC12" s="47">
+      <c r="AC12" s="34">
         <v>0.3</v>
       </c>
-      <c r="AD12" s="44" t="str">
+      <c r="AD12" s="31" t="str">
         <f>CONCATENATE("stat(bullet_velocity;",'545-ammo'!$AE12,";",'545-ammo'!$AF12,";",'545-ammo'!$AG12,";",'545-ammo'!$AH12,")")</f>
         <v>stat(bullet_velocity;0.1;0.6;500;2000)</v>
       </c>
-      <c r="AE12" s="47">
+      <c r="AE12" s="34">
         <v>0.1</v>
       </c>
-      <c r="AF12" s="47">
+      <c r="AF12" s="34">
         <v>0.6</v>
       </c>
-      <c r="AG12" s="49">
-        <v>500.0</v>
-      </c>
-      <c r="AH12" s="49">
-        <v>2000.0</v>
-      </c>
-      <c r="AI12" s="50">
+      <c r="AG12" s="36">
+        <v>500</v>
+      </c>
+      <c r="AH12" s="36">
+        <v>2000</v>
+      </c>
+      <c r="AI12" s="37">
         <f>Model!$B$4+IF(I12="",0,I12)</f>
         <v>1439</v>
       </c>
-      <c r="AJ12" s="46">
-        <f t="shared" si="1"/>
-        <v>0.413</v>
-      </c>
-      <c r="AK12" s="51">
-        <v>66.0</v>
-      </c>
-      <c r="AL12" s="52" t="s">
+      <c r="AJ12" s="33">
+        <f t="shared" si="0"/>
+        <v>0.41300000000000003</v>
+      </c>
+      <c r="AK12" s="38">
+        <v>66</v>
+      </c>
+      <c r="AL12" s="39" t="s">
         <v>86</v>
       </c>
-      <c r="AM12" s="53">
+      <c r="AM12" s="40">
         <f>C12*Model!$B$24+D12*Model!$B$25+E12*Model!$B$26+F12*Model!$B$27+G12*Model!$B$28+H12*Model!$B$29+I12*Model!$B$30+J12*Model!$B$31+K12*Model!$B$32+L12*Model!$B$33</f>
-        <v>4.7</v>
-      </c>
-      <c r="AN12" s="53">
+        <v>4.6999999999999993</v>
+      </c>
+      <c r="AN12" s="40">
         <f>(AA12-Model!$B$5)*Model!$B$36</f>
-        <v>-4.26</v>
-      </c>
-      <c r="AO12" s="53">
+        <v>-4.2599999999999945</v>
+      </c>
+      <c r="AO12" s="40">
         <f>(Model!$B$6-AB12)*Model!$B$37</f>
-        <v>-0.1</v>
-      </c>
-      <c r="AP12" s="53">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="AP12" s="40">
         <f>(AC12-Model!$B$7)*Model!$B$38</f>
-        <v>-0.3</v>
-      </c>
-      <c r="AQ12" s="53">
+        <v>-0.3000000000000001</v>
+      </c>
+      <c r="AQ12" s="40">
         <f>(AJ12-Model!$B$8)*Model!$B$39</f>
         <v>1.052</v>
       </c>
-      <c r="AR12" s="53">
-        <f t="shared" si="2"/>
-        <v>1.092</v>
+      <c r="AR12" s="40">
+        <f t="shared" si="1"/>
+        <v>1.2920000000000049</v>
       </c>
     </row>
-    <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="56" t="s">
+    <row r="13" spans="1:44" ht="14.25" customHeight="1">
+      <c r="A13" s="43" t="s">
         <v>105</v>
       </c>
-      <c r="B13" s="56" t="s">
+      <c r="B13" s="43" t="s">
         <v>106</v>
       </c>
-      <c r="C13" s="59">
-        <v>-2.0</v>
-      </c>
-      <c r="D13" s="58">
+      <c r="C13" s="46">
+        <v>-2</v>
+      </c>
+      <c r="D13" s="45">
         <v>-0.12</v>
       </c>
-      <c r="E13" s="59">
-        <v>-1.0</v>
-      </c>
-      <c r="F13" s="57">
-        <v>0.0</v>
-      </c>
-      <c r="G13" s="58">
+      <c r="E13" s="46">
+        <v>-1</v>
+      </c>
+      <c r="F13" s="44">
+        <v>0</v>
+      </c>
+      <c r="G13" s="45">
         <v>-0.15</v>
       </c>
-      <c r="H13" s="61"/>
-      <c r="I13" s="59">
-        <v>500.0</v>
-      </c>
-      <c r="J13" s="60"/>
-      <c r="K13" s="62"/>
-      <c r="L13" s="62">
-        <v>2500.0</v>
-      </c>
-      <c r="M13" s="64">
-        <v>-0.058</v>
-      </c>
-      <c r="N13" s="64">
+      <c r="H13" s="48"/>
+      <c r="I13" s="46">
+        <v>500</v>
+      </c>
+      <c r="J13" s="47"/>
+      <c r="K13" s="49"/>
+      <c r="L13" s="49">
+        <v>2500</v>
+      </c>
+      <c r="M13" s="51">
+        <v>-5.8000000000000003E-2</v>
+      </c>
+      <c r="N13" s="51">
         <v>36.5</v>
       </c>
-      <c r="O13" s="64">
+      <c r="O13" s="51">
         <v>35.5</v>
       </c>
-      <c r="P13" s="64">
-        <v>1.0</v>
-      </c>
-      <c r="Q13" s="45">
+      <c r="P13" s="51">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="32">
         <v>0.25</v>
       </c>
-      <c r="R13" s="45">
+      <c r="R13" s="32">
         <v>0.45</v>
       </c>
-      <c r="S13" s="44">
-        <v>3.0</v>
-      </c>
-      <c r="T13" s="65">
+      <c r="S13" s="31">
+        <v>3</v>
+      </c>
+      <c r="T13" s="52">
         <f>MAX(MIN($M13*Model!$A$13+$N13,$O13)*$P13,0)</f>
-        <v>35.05</v>
-      </c>
-      <c r="U13" s="65">
+        <v>35.049999999999997</v>
+      </c>
+      <c r="U13" s="52">
         <f>MAX(MIN($M13*Model!$A$14+$N13,$O13)*$P13,0)</f>
         <v>32.15</v>
       </c>
-      <c r="V13" s="65">
+      <c r="V13" s="52">
         <f>MAX(MIN($M13*Model!$A$15+$N13,$O13)*$P13,0)</f>
-        <v>27.8</v>
-      </c>
-      <c r="W13" s="65">
+        <v>27.799999999999997</v>
+      </c>
+      <c r="W13" s="52">
         <f>MAX(MIN($M13*Model!$A$16+$N13,$O13)*$P13,0)</f>
         <v>22</v>
       </c>
-      <c r="X13" s="65">
+      <c r="X13" s="52">
         <f>MAX(MIN($M13*Model!$A$17+$N13,$O13)*$P13,0)</f>
         <v>35.5</v>
       </c>
-      <c r="Y13" s="65">
+      <c r="Y13" s="52">
         <f>MAX(MIN($M13*Model!$A$18+$N13,$O13)*$P13,0)</f>
         <v>35.5</v>
       </c>
-      <c r="Z13" s="65">
+      <c r="Z13" s="52">
         <f>MAX(MIN($M13*Model!$A$19+$N13,$O13)*$P13,0)</f>
         <v>35.5</v>
       </c>
-      <c r="AA13" s="65">
+      <c r="AA13" s="52">
         <f>T13*Model!$B$13+U13*Model!$B$14+V13*Model!$B$15+W13*Model!$B$16+X13*Model!$B$17+Y13*Model!$B$18+Z13*Model!$B$19</f>
-        <v>30.41</v>
-      </c>
-      <c r="AB13" s="66">
+        <v>30.409999999999997</v>
+      </c>
+      <c r="AB13" s="53">
         <v>0.7</v>
       </c>
-      <c r="AC13" s="66">
+      <c r="AC13" s="53">
         <v>0.3</v>
       </c>
-      <c r="AD13" s="44" t="str">
+      <c r="AD13" s="31" t="str">
         <f>CONCATENATE("stat(bullet_velocity;",'545-ammo'!$AE13,";",'545-ammo'!$AF13,";",'545-ammo'!$AG13,";",'545-ammo'!$AH13,")")</f>
         <v>stat(bullet_velocity;0.15;0.65;500;2000)</v>
       </c>
-      <c r="AE13" s="66">
+      <c r="AE13" s="53">
         <v>0.15</v>
       </c>
-      <c r="AF13" s="66">
+      <c r="AF13" s="53">
         <v>0.65</v>
       </c>
-      <c r="AG13" s="49">
-        <v>500.0</v>
-      </c>
-      <c r="AH13" s="49">
-        <v>2000.0</v>
-      </c>
-      <c r="AI13" s="67">
+      <c r="AG13" s="36">
+        <v>500</v>
+      </c>
+      <c r="AH13" s="36">
+        <v>2000</v>
+      </c>
+      <c r="AI13" s="54">
         <f>Model!$B$4+IF(I13="",0,I13)</f>
         <v>1639</v>
       </c>
-      <c r="AJ13" s="65">
-        <f t="shared" si="1"/>
-        <v>0.5296666667</v>
-      </c>
-      <c r="AK13" s="68">
-        <v>68.0</v>
-      </c>
-      <c r="AL13" s="69" t="s">
+      <c r="AJ13" s="52">
+        <f t="shared" si="0"/>
+        <v>0.52966666666666662</v>
+      </c>
+      <c r="AK13" s="55">
+        <v>68</v>
+      </c>
+      <c r="AL13" s="56" t="s">
         <v>86</v>
       </c>
-      <c r="AM13" s="53">
+      <c r="AM13" s="40">
         <f>C13*Model!$B$24+D13*Model!$B$25+E13*Model!$B$26+F13*Model!$B$27+G13*Model!$B$28+H13*Model!$B$29+I13*Model!$B$30+J13*Model!$B$31+K13*Model!$B$32+L13*Model!$B$33</f>
         <v>5.2</v>
       </c>
-      <c r="AN13" s="70">
+      <c r="AN13" s="57">
         <f>(AA13-Model!$B$5)*Model!$B$36</f>
-        <v>-4.38</v>
-      </c>
-      <c r="AO13" s="70">
+        <v>-4.3800000000000026</v>
+      </c>
+      <c r="AO13" s="57">
         <f>(Model!$B$6-AB13)*Model!$B$37</f>
-        <v>-0.2</v>
-      </c>
-      <c r="AP13" s="70">
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AP13" s="57">
         <f>(AC13-Model!$B$7)*Model!$B$38</f>
-        <v>-0.3</v>
-      </c>
-      <c r="AQ13" s="70">
+        <v>-0.3000000000000001</v>
+      </c>
+      <c r="AQ13" s="57">
         <f>(AJ13-Model!$B$8)*Model!$B$39</f>
-        <v>1.518666667</v>
-      </c>
-      <c r="AR13" s="70">
-        <f t="shared" si="2"/>
-        <v>1.838666667</v>
+        <v>1.5186666666666664</v>
+      </c>
+      <c r="AR13" s="57">
+        <f t="shared" si="1"/>
+        <v>2.2386666666666639</v>
       </c>
     </row>
-    <row r="14" ht="14.25" customHeight="1"/>
-    <row r="15" ht="14.25" customHeight="1"/>
-    <row r="16" ht="14.25" customHeight="1"/>
+    <row r="14" spans="1:44" ht="14.25" customHeight="1"/>
+    <row r="15" spans="1:44" ht="14.25" customHeight="1"/>
+    <row r="16" spans="1:44" ht="14.25" customHeight="1"/>
     <row r="17" ht="14.25" customHeight="1"/>
     <row r="18" ht="14.25" customHeight="1"/>
     <row r="19" ht="14.25" customHeight="1"/>
@@ -3919,13 +3966,13 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="AK1:AL1"/>
+    <mergeCell ref="AM1:AR1"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="M1:P1"/>
     <mergeCell ref="T1:AA1"/>
     <mergeCell ref="AB1:AH1"/>
     <mergeCell ref="AI1:AJ1"/>
-    <mergeCell ref="AK1:AL1"/>
-    <mergeCell ref="AM1:AR1"/>
   </mergeCells>
   <conditionalFormatting sqref="AR3:AR13">
     <cfRule type="colorScale" priority="1">
@@ -3939,420 +3986,416 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <legacyDrawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:C1001"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="30.0"/>
-    <col customWidth="1" min="2" max="2" width="16.0"/>
-    <col customWidth="1" min="3" max="3" width="42.0"/>
-    <col customWidth="1" min="4" max="26" width="8.63"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="4" max="26" width="8.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" ht="31.5" customHeight="1">
+      <c r="A1" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="3"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="60"/>
     </row>
-    <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
+    <row r="2" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
     </row>
-    <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="7">
-        <v>1139.0</v>
-      </c>
-      <c r="C4" s="8" t="s">
+      <c r="B4" s="4">
+        <v>1139</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="9" t="s">
+    <row r="5" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A5" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="7">
         <v>33.33</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="9" t="s">
+    <row r="6" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A6" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="8">
         <v>0.6</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="9" t="s">
+    <row r="7" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="8">
         <v>0.4</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="8">
         <v>0.15</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
+    <row r="9" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
     </row>
-    <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="13" t="s">
+    <row r="10" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A10" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="14"/>
-      <c r="C10" s="15"/>
+      <c r="B10" s="62"/>
+      <c r="C10" s="63"/>
     </row>
-    <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
+    <row r="11" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
     </row>
-    <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="17" t="s">
+    <row r="12" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A12" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="19">
-        <v>25.0</v>
-      </c>
-      <c r="B13" s="20">
+    <row r="13" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A13" s="11">
+        <v>25</v>
+      </c>
+      <c r="B13" s="12">
         <v>0.3</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="19">
-        <v>75.0</v>
-      </c>
-      <c r="B14" s="20">
+    <row r="14" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A14" s="11">
+        <v>75</v>
+      </c>
+      <c r="B14" s="12">
         <v>0.3</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="19">
-        <v>150.0</v>
-      </c>
-      <c r="B15" s="20">
+    <row r="15" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A15" s="11">
+        <v>150</v>
+      </c>
+      <c r="B15" s="12">
         <v>0.25</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="19">
-        <v>250.0</v>
-      </c>
-      <c r="B16" s="20">
+    <row r="16" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A16" s="11">
+        <v>250</v>
+      </c>
+      <c r="B16" s="12">
         <v>0.15</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="11" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="22">
-        <v>0.0</v>
-      </c>
-      <c r="B17" s="23">
-        <v>0.0</v>
-      </c>
-      <c r="C17" s="19" t="s">
+    <row r="17" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A17" s="13">
+        <v>0</v>
+      </c>
+      <c r="B17" s="14">
+        <v>0</v>
+      </c>
+      <c r="C17" s="11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="22">
-        <v>0.0</v>
-      </c>
-      <c r="B18" s="23">
-        <v>0.0</v>
-      </c>
-      <c r="C18" s="19" t="s">
+    <row r="18" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A18" s="13">
+        <v>0</v>
+      </c>
+      <c r="B18" s="14">
+        <v>0</v>
+      </c>
+      <c r="C18" s="11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="22">
-        <v>0.0</v>
-      </c>
-      <c r="B19" s="23">
-        <v>0.0</v>
-      </c>
-      <c r="C19" s="19" t="s">
+    <row r="19" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A19" s="13">
+        <v>0</v>
+      </c>
+      <c r="B19" s="14">
+        <v>0</v>
+      </c>
+      <c r="C19" s="11" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="19" t="s">
+    <row r="20" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A20" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="23">
+      <c r="B20" s="14">
         <f>SUM(B13:B19)</f>
         <v>1</v>
       </c>
-      <c r="C20" s="19"/>
+      <c r="C20" s="11"/>
     </row>
-    <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
+    <row r="21" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
     </row>
-    <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="13" t="s">
+    <row r="22" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A22" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="15"/>
+      <c r="B22" s="62"/>
+      <c r="C22" s="63"/>
     </row>
-    <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="17" t="s">
+    <row r="23" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A23" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="C23" s="9" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" s="19" t="s">
+    <row r="24" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A24" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B24" s="27">
-        <v>1.0</v>
-      </c>
-      <c r="C24" s="19" t="s">
+      <c r="B24" s="15">
+        <v>1</v>
+      </c>
+      <c r="C24" s="11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" s="19" t="s">
+    <row r="25" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A25" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="27">
-        <v>-20.0</v>
-      </c>
-      <c r="C25" s="19" t="s">
+      <c r="B25" s="15">
+        <v>-20</v>
+      </c>
+      <c r="C25" s="11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="19" t="s">
+    <row r="26" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A26" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="27">
+      <c r="B26" s="15">
         <v>-0.8</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="C26" s="11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" s="19" t="s">
+    <row r="27" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A27" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="27">
+      <c r="B27" s="15">
         <v>-0.6</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="C27" s="11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="19" t="s">
+    <row r="28" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A28" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="27">
-        <v>-10.0</v>
-      </c>
-      <c r="C28" s="19" t="s">
+      <c r="B28" s="15">
+        <v>-10</v>
+      </c>
+      <c r="C28" s="11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="19" t="s">
+    <row r="29" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A29" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="27">
-        <v>10.0</v>
-      </c>
-      <c r="C29" s="19" t="s">
+      <c r="B29" s="15">
+        <v>10</v>
+      </c>
+      <c r="C29" s="11" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" s="19" t="s">
+    <row r="30" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A30" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B30" s="29">
-        <v>0.005</v>
-      </c>
-      <c r="C30" s="19" t="str">
-        <f>CONCAT("1 point per +", 1/B30, " vel")</f>
-        <v>#N/A</v>
+      <c r="B30" s="17">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C30" s="11" t="e">
+        <f ca="1">_xludf.CONCAT("1 point per +", 1/B30, " vel")</f>
+        <v>#NAME?</v>
       </c>
     </row>
-    <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" s="19" t="s">
+    <row r="31" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A31" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B31" s="27">
-        <v>10.0</v>
-      </c>
-      <c r="C31" s="19" t="s">
+      <c r="B31" s="15">
+        <v>10</v>
+      </c>
+      <c r="C31" s="11" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="32" ht="14.25" customHeight="1">
-      <c r="A32" s="22" t="s">
+    <row r="32" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A32" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="B32" s="30">
-        <v>-5.0</v>
-      </c>
-      <c r="C32" s="19"/>
+      <c r="B32" s="18">
+        <v>-5</v>
+      </c>
+      <c r="C32" s="11"/>
     </row>
-    <row r="33" ht="14.25" customHeight="1">
-      <c r="A33" s="19" t="s">
+    <row r="33" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A33" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B33" s="27">
-        <v>0.0</v>
-      </c>
-      <c r="C33" s="19" t="s">
+      <c r="B33" s="15">
+        <v>0</v>
+      </c>
+      <c r="C33" s="11" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="34" ht="14.25" customHeight="1">
-      <c r="A34" s="8"/>
-      <c r="B34" s="32"/>
-      <c r="C34" s="8"/>
+    <row r="34" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A34" s="5"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="5"/>
     </row>
-    <row r="35" ht="14.25" customHeight="1">
-      <c r="A35" s="13" t="s">
+    <row r="35" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A35" s="61" t="s">
         <v>48</v>
       </c>
-      <c r="B35" s="14"/>
-      <c r="C35" s="15"/>
+      <c r="B35" s="62"/>
+      <c r="C35" s="63"/>
     </row>
-    <row r="36" ht="14.25" customHeight="1">
-      <c r="A36" s="33" t="s">
+    <row r="36" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A36" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="B36" s="34">
+      <c r="B36" s="22">
         <v>1.5</v>
       </c>
-      <c r="C36" s="33" t="s">
+      <c r="C36" s="21" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="37" ht="14.25" customHeight="1">
-      <c r="A37" s="33" t="s">
+    <row r="37" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A37" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="B37" s="34">
-        <v>2.0</v>
-      </c>
-      <c r="C37" s="33" t="s">
+      <c r="B37" s="22">
+        <v>-2</v>
+      </c>
+      <c r="C37" s="21" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="38" ht="14.25" customHeight="1">
-      <c r="A38" s="33" t="s">
+    <row r="38" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A38" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="B38" s="34">
-        <v>3.0</v>
-      </c>
-      <c r="C38" s="33" t="s">
+      <c r="B38" s="22">
+        <v>3</v>
+      </c>
+      <c r="C38" s="21" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="39" ht="14.25" customHeight="1">
-      <c r="A39" s="35" t="s">
+    <row r="39" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A39" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="B39" s="36">
-        <v>4.0</v>
-      </c>
-      <c r="C39" s="35" t="s">
+      <c r="B39" s="24">
+        <v>4</v>
+      </c>
+      <c r="C39" s="23" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="40" ht="14.25" customHeight="1"/>
-    <row r="41" ht="14.25" customHeight="1"/>
-    <row r="42" ht="14.25" customHeight="1"/>
-    <row r="43" ht="14.25" customHeight="1"/>
-    <row r="44" ht="14.25" customHeight="1"/>
-    <row r="45" ht="14.25" customHeight="1"/>
-    <row r="46" ht="14.25" customHeight="1"/>
-    <row r="47" ht="14.25" customHeight="1"/>
-    <row r="48" ht="14.25" customHeight="1"/>
+    <row r="40" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="41" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="42" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="43" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="44" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="45" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="46" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="47" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="48" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="49" ht="14.25" customHeight="1"/>
     <row r="50" ht="14.25" customHeight="1"/>
     <row r="51" ht="14.25" customHeight="1"/>
@@ -5313,10 +5356,8 @@
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A35:C35"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>